--- a/inasistencias-4b-tc/alumnos-4b-tc.xlsx
+++ b/inasistencias-4b-tc/alumnos-4b-tc.xlsx
@@ -8,15 +8,15 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="asistencia" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="notas" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="1_atomo" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="2-coulomb" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="3-Cap2-3" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="4-cap 4-5-6" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="5-thevenin" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="positivos" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="Evaluacion" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="notas" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="1_atomo" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="2-coulomb" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="3-Cap2-3" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="4-cap 4-5-6" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="5-thevenin" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="positivos" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Evaluacion" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="271">
   <si>
     <t xml:space="preserve">total</t>
   </si>
@@ -938,8 +938,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -947,35 +971,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1091,1720 +1107,1897 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AH22"/>
-  <sheetFormatPr defaultColWidth="8.78125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AJ22"/>
+  <sheetFormatPr defaultColWidth="8.7890625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.2"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="0" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.47"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="0" width="31.19"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="5" style="0" width="8.62"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="7" style="0" width="11.07"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="8" style="0" width="8.62"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="0" width="11.84"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="11" style="0" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="15" min="15" style="0" width="11.36"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="16" style="0" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.47"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="31.19"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="5" style="1" width="8.62"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="7" style="1" width="11.07"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="8" style="1" width="8.62"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="1" width="11.84"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="11" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="15" min="15" style="1" width="11.36"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="16" style="1" width="8.67"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="33" min="25" style="0" width="8.79"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="V1" s="3"/>
-      <c r="Z1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA1" s="0" t="n">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="V1" s="4"/>
+      <c r="Z1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="1" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>45785</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>45792</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>45799</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="3" t="n">
         <v>45813</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>45820</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="3" t="n">
         <v>45827</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="M2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="3" t="n">
         <v>45834</v>
       </c>
-      <c r="O2" s="0" t="s">
+      <c r="O2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="P2" s="3" t="n">
         <v>45841</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q2" s="3" t="n">
         <v>45848</v>
       </c>
-      <c r="R2" s="0" t="s">
+      <c r="R2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="0" t="s">
+      <c r="S2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="0" t="s">
+      <c r="T2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="0" t="s">
+      <c r="U2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="V2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="W2" s="0" t="s">
+      <c r="W2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="X2" s="0" t="s">
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="Y2" s="2" t="n">
+      <c r="Y2" s="3" t="n">
         <v>45855</v>
       </c>
-      <c r="Z2" s="0" t="s">
+      <c r="Z2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AA2" s="2" t="n">
+      <c r="AA2" s="3" t="n">
         <v>45897</v>
       </c>
-      <c r="AB2" s="0" t="s">
+      <c r="AB2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AC2" s="2" t="n">
+      <c r="AC2" s="3" t="n">
         <v>45904</v>
       </c>
-      <c r="AD2" s="2" t="n">
+      <c r="AD2" s="3" t="n">
         <v>45918</v>
       </c>
-      <c r="AE2" s="0" t="s">
+      <c r="AE2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AF2" s="2" t="n">
+      <c r="AF2" s="3" t="n">
         <v>45925</v>
       </c>
-      <c r="AG2" s="0" t="s">
+      <c r="AG2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AH2" s="2" t="n">
+      <c r="AH2" s="3" t="n">
         <v>45932</v>
       </c>
+      <c r="AI2" s="5" t="n">
+        <v>45953</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" s="0" t="s">
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="0" t="s">
+      <c r="O3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q3" s="0" t="s">
+      <c r="P3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="3" t="n">
+      <c r="R3" s="4" t="n">
         <v>0.541666666666667</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="S3" s="1" t="n">
         <f aca="false">COUNTIF(E3:Q3,"E")</f>
         <v>1</v>
       </c>
-      <c r="T3" s="0" t="n">
+      <c r="T3" s="1" t="n">
         <f aca="false">COUNTIF(E3:Q3,"P")</f>
         <v>7</v>
       </c>
-      <c r="U3" s="0" t="n">
+      <c r="U3" s="1" t="n">
         <f aca="false">COUNTIF(E3:Q3,"M")</f>
         <v>0</v>
       </c>
-      <c r="V3" s="0" t="n">
+      <c r="V3" s="1" t="n">
         <f aca="false">COUNTIF(E3:Q3,"T")</f>
         <v>1</v>
       </c>
-      <c r="W3" s="0" t="n">
+      <c r="W3" s="1" t="n">
         <f aca="false">ROUND(T3+U3/2+V3/4,0)</f>
         <v>7</v>
       </c>
-      <c r="X3" s="5" t="n">
+      <c r="X3" s="6" t="n">
         <f aca="false">ROUND(W3*10/$AA$1,0)</f>
         <v>8</v>
       </c>
-      <c r="Y3" s="0" t="s">
+      <c r="Y3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="3" t="n">
+      <c r="Z3" s="4" t="n">
         <v>0.520833333333333</v>
       </c>
-      <c r="AA3" s="0" t="s">
+      <c r="AA3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AB3" s="3" t="n">
+      <c r="AB3" s="4" t="n">
         <v>0.527777777777778</v>
       </c>
-      <c r="AC3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH3" s="0" t="s">
-        <v>15</v>
+      <c r="AC3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ3" s="8" t="n">
+        <v>0.538194444444444</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" s="0" t="s">
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="S4" s="4" t="n">
+      <c r="P4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S4" s="1" t="n">
         <f aca="false">COUNTIF(E4:Q4,"E")</f>
         <v>0</v>
       </c>
-      <c r="T4" s="0" t="n">
+      <c r="T4" s="1" t="n">
         <f aca="false">COUNTIF(E4:Q4,"P")</f>
         <v>7</v>
       </c>
-      <c r="U4" s="0" t="n">
+      <c r="U4" s="1" t="n">
         <f aca="false">COUNTIF(E4:Q4,"M")</f>
         <v>0</v>
       </c>
-      <c r="V4" s="0" t="n">
+      <c r="V4" s="1" t="n">
         <f aca="false">COUNTIF(E4:Q4,"T")</f>
         <v>0</v>
       </c>
-      <c r="W4" s="0" t="n">
+      <c r="W4" s="1" t="n">
         <f aca="false">ROUND(T4+U4/2+V4/4,0)</f>
         <v>7</v>
       </c>
-      <c r="X4" s="5" t="n">
+      <c r="X4" s="6" t="n">
         <f aca="false">ROUND(W4*10/$AA$1,0)</f>
         <v>8</v>
       </c>
-      <c r="Y4" s="0" t="s">
+      <c r="Y4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Z4" s="3" t="n">
+      <c r="Z4" s="4" t="n">
         <v>0.513888888888889</v>
       </c>
-      <c r="AA4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF4" s="0" t="s">
+      <c r="AA4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH4" s="0" t="s">
+      <c r="AH4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI4" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="N5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="P5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="S5" s="4" t="n">
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S5" s="1" t="n">
         <f aca="false">COUNTIF(E5:Q5,"E")</f>
         <v>0</v>
       </c>
-      <c r="T5" s="0" t="n">
+      <c r="T5" s="1" t="n">
         <f aca="false">COUNTIF(E5:Q5,"P")</f>
         <v>9</v>
       </c>
-      <c r="U5" s="0" t="n">
+      <c r="U5" s="1" t="n">
         <f aca="false">COUNTIF(E5:Q5,"M")</f>
         <v>0</v>
       </c>
-      <c r="V5" s="0" t="n">
+      <c r="V5" s="1" t="n">
         <f aca="false">COUNTIF(E5:Q5,"T")</f>
         <v>0</v>
       </c>
-      <c r="W5" s="0" t="n">
+      <c r="W5" s="1" t="n">
         <f aca="false">ROUND(T5+U5/2+V5/4,0)</f>
         <v>9</v>
       </c>
-      <c r="X5" s="5" t="n">
+      <c r="X5" s="6" t="n">
         <f aca="false">ROUND(W5*10/$AA$1,0)</f>
         <v>10</v>
       </c>
-      <c r="Y5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH5" s="0" t="s">
+      <c r="Y5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI5" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="L6" s="0" t="s">
+      <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="0" t="s">
+      <c r="M6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="P6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="S6" s="4" t="n">
+      <c r="N6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S6" s="1" t="n">
         <f aca="false">COUNTIF(E6:Q6,"E")</f>
         <v>1</v>
       </c>
-      <c r="T6" s="0" t="n">
+      <c r="T6" s="1" t="n">
         <f aca="false">COUNTIF(E6:Q6,"P")</f>
         <v>8</v>
       </c>
-      <c r="U6" s="0" t="n">
+      <c r="U6" s="1" t="n">
         <f aca="false">COUNTIF(E6:Q6,"M")</f>
         <v>0</v>
       </c>
-      <c r="V6" s="0" t="n">
+      <c r="V6" s="1" t="n">
         <f aca="false">COUNTIF(E6:Q6,"T")</f>
         <v>0</v>
       </c>
-      <c r="W6" s="0" t="n">
+      <c r="W6" s="1" t="n">
         <f aca="false">ROUND(T6+U6/2+V6/4,0)</f>
         <v>8</v>
       </c>
-      <c r="X6" s="5" t="n">
+      <c r="X6" s="6" t="n">
         <f aca="false">ROUND(W6*10/$AA$1,0)</f>
         <v>9</v>
       </c>
-      <c r="Y6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF6" s="0" t="s">
+      <c r="Y6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH6" s="0" t="s">
+      <c r="AH6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI6" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="N7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="P7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="S7" s="4" t="n">
+      <c r="E7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S7" s="1" t="n">
         <f aca="false">COUNTIF(E7:Q7,"E")</f>
         <v>0</v>
       </c>
-      <c r="T7" s="0" t="n">
+      <c r="T7" s="1" t="n">
         <f aca="false">COUNTIF(E7:Q7,"P")</f>
         <v>9</v>
       </c>
-      <c r="U7" s="0" t="n">
+      <c r="U7" s="1" t="n">
         <f aca="false">COUNTIF(E7:Q7,"M")</f>
         <v>0</v>
       </c>
-      <c r="V7" s="0" t="n">
+      <c r="V7" s="1" t="n">
         <f aca="false">COUNTIF(E7:Q7,"T")</f>
         <v>0</v>
       </c>
-      <c r="W7" s="0" t="n">
+      <c r="W7" s="1" t="n">
         <f aca="false">ROUND(T7+U7/2+V7/4,0)</f>
         <v>9</v>
       </c>
-      <c r="X7" s="5" t="n">
+      <c r="X7" s="6" t="n">
         <f aca="false">ROUND(W7*10/$AA$1,0)</f>
         <v>10</v>
       </c>
-      <c r="Y7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF7" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH7" s="0" t="s">
+      <c r="Y7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI7" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="N8" s="0" t="s">
+      <c r="E8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="S8" s="4" t="n">
+      <c r="P8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S8" s="1" t="n">
         <f aca="false">COUNTIF(E8:Q8,"E")</f>
         <v>0</v>
       </c>
-      <c r="T8" s="0" t="n">
+      <c r="T8" s="1" t="n">
         <f aca="false">COUNTIF(E8:Q8,"P")</f>
         <v>8</v>
       </c>
-      <c r="U8" s="0" t="n">
+      <c r="U8" s="1" t="n">
         <f aca="false">COUNTIF(E8:Q8,"M")</f>
         <v>0</v>
       </c>
-      <c r="V8" s="0" t="n">
+      <c r="V8" s="1" t="n">
         <f aca="false">COUNTIF(E8:Q8,"T")</f>
         <v>0</v>
       </c>
-      <c r="W8" s="0" t="n">
+      <c r="W8" s="1" t="n">
         <f aca="false">ROUND(T8+U8/2+V8/4,0)</f>
         <v>8</v>
       </c>
-      <c r="X8" s="5" t="n">
+      <c r="X8" s="6" t="n">
         <f aca="false">ROUND(W8*10/$AA$1,0)</f>
         <v>9</v>
       </c>
-      <c r="Y8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH8" s="0" t="s">
+      <c r="Y8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI8" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="0" t="s">
+      <c r="E9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="0" t="s">
+      <c r="I9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="0" t="s">
+      <c r="J9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="N9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="P9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="S9" s="4" t="n">
+      <c r="K9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S9" s="1" t="n">
         <f aca="false">COUNTIF(E9:Q9,"E")</f>
         <v>1</v>
       </c>
-      <c r="T9" s="0" t="n">
+      <c r="T9" s="1" t="n">
         <f aca="false">COUNTIF(E9:Q9,"P")</f>
         <v>7</v>
       </c>
-      <c r="U9" s="0" t="n">
+      <c r="U9" s="1" t="n">
         <f aca="false">COUNTIF(E9:Q9,"M")</f>
         <v>0</v>
       </c>
-      <c r="V9" s="0" t="n">
+      <c r="V9" s="1" t="n">
         <f aca="false">COUNTIF(E9:Q9,"T")</f>
         <v>0</v>
       </c>
-      <c r="W9" s="0" t="n">
+      <c r="W9" s="1" t="n">
         <f aca="false">ROUND(T9+U9/2+V9/4,0)</f>
         <v>7</v>
       </c>
-      <c r="X9" s="5" t="n">
+      <c r="X9" s="6" t="n">
         <f aca="false">ROUND(W9*10/$AA$1,0)</f>
         <v>8</v>
       </c>
-      <c r="Y9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA9" s="0" t="s">
+      <c r="Y9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AB9" s="3" t="n">
+      <c r="AB9" s="4" t="n">
         <v>0.520833333333333</v>
       </c>
-      <c r="AC9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH9" s="0" t="s">
+      <c r="AC9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI9" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="0" t="s">
+      <c r="E10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="L10" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="N10" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="P10" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q10" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="S10" s="4" t="n">
+      <c r="I10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S10" s="1" t="n">
         <f aca="false">COUNTIF(E10:Q10,"E")</f>
         <v>0</v>
       </c>
-      <c r="T10" s="0" t="n">
+      <c r="T10" s="1" t="n">
         <f aca="false">COUNTIF(E10:Q10,"P")</f>
         <v>8</v>
       </c>
-      <c r="U10" s="0" t="n">
+      <c r="U10" s="1" t="n">
         <f aca="false">COUNTIF(E10:Q10,"M")</f>
         <v>0</v>
       </c>
-      <c r="V10" s="0" t="n">
+      <c r="V10" s="1" t="n">
         <f aca="false">COUNTIF(E10:Q10,"T")</f>
         <v>0</v>
       </c>
-      <c r="W10" s="0" t="n">
+      <c r="W10" s="1" t="n">
         <f aca="false">ROUND(T10+U10/2+V10/4,0)</f>
         <v>8</v>
       </c>
-      <c r="X10" s="5" t="n">
+      <c r="X10" s="6" t="n">
         <f aca="false">ROUND(W10*10/$AA$1,0)</f>
         <v>9</v>
       </c>
-      <c r="Y10" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA10" s="0" t="s">
+      <c r="Y10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AC10" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD10" s="0" t="s">
+      <c r="AC10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AF10" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH10" s="0" t="s">
+      <c r="AF10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI10" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="N11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="P11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="S11" s="4" t="n">
+      <c r="E11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1" t="n">
         <f aca="false">COUNTIF(E11:Q11,"E")</f>
         <v>0</v>
       </c>
-      <c r="T11" s="0" t="n">
+      <c r="T11" s="1" t="n">
         <f aca="false">COUNTIF(E11:Q11,"P")</f>
         <v>9</v>
       </c>
-      <c r="U11" s="0" t="n">
+      <c r="U11" s="1" t="n">
         <f aca="false">COUNTIF(E11:Q11,"M")</f>
         <v>0</v>
       </c>
-      <c r="V11" s="0" t="n">
+      <c r="V11" s="1" t="n">
         <f aca="false">COUNTIF(E11:Q11,"T")</f>
         <v>0</v>
       </c>
-      <c r="W11" s="0" t="n">
+      <c r="W11" s="1" t="n">
         <f aca="false">ROUND(T11+U11/2+V11/4,0)</f>
         <v>9</v>
       </c>
-      <c r="X11" s="5" t="n">
+      <c r="X11" s="6" t="n">
         <f aca="false">ROUND(W11*10/$AA$1,0)</f>
         <v>10</v>
       </c>
-      <c r="Y11" s="0" t="s">
+      <c r="Y11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AA11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH11" s="0" t="s">
+      <c r="AA11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI11" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="K12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="N12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="P12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="S12" s="4" t="n">
+      <c r="E12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S12" s="1" t="n">
         <f aca="false">COUNTIF(E12:Q12,"E")</f>
         <v>0</v>
       </c>
-      <c r="T12" s="0" t="n">
+      <c r="T12" s="1" t="n">
         <f aca="false">COUNTIF(E12:Q12,"P")</f>
         <v>9</v>
       </c>
-      <c r="U12" s="0" t="n">
+      <c r="U12" s="1" t="n">
         <f aca="false">COUNTIF(E12:Q12,"M")</f>
         <v>0</v>
       </c>
-      <c r="V12" s="0" t="n">
+      <c r="V12" s="1" t="n">
         <f aca="false">COUNTIF(E12:Q12,"T")</f>
         <v>0</v>
       </c>
-      <c r="W12" s="0" t="n">
+      <c r="W12" s="1" t="n">
         <f aca="false">ROUND(T12+U12/2+V12/4,0)</f>
         <v>9</v>
       </c>
-      <c r="X12" s="5" t="n">
+      <c r="X12" s="6" t="n">
         <f aca="false">ROUND(W12*10/$AA$1,0)</f>
         <v>10</v>
       </c>
-      <c r="Y12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH12" s="0" t="s">
+      <c r="Y12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI12" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="0" t="s">
+      <c r="E13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" s="4" t="n">
         <v>0.53125</v>
       </c>
-      <c r="K13" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="N13" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="P13" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q13" s="0" t="s">
+      <c r="K13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="S13" s="4" t="n">
+      <c r="S13" s="1" t="n">
         <f aca="false">COUNTIF(E13:Q13,"E")</f>
         <v>0</v>
       </c>
-      <c r="T13" s="0" t="n">
+      <c r="T13" s="1" t="n">
         <f aca="false">COUNTIF(E13:Q13,"P")</f>
         <v>7</v>
       </c>
-      <c r="U13" s="0" t="n">
+      <c r="U13" s="1" t="n">
         <f aca="false">COUNTIF(E13:Q13,"M")</f>
         <v>0</v>
       </c>
-      <c r="V13" s="0" t="n">
+      <c r="V13" s="1" t="n">
         <f aca="false">COUNTIF(E13:Q13,"T")</f>
         <v>1</v>
       </c>
-      <c r="W13" s="0" t="n">
+      <c r="W13" s="1" t="n">
         <f aca="false">ROUND(T13+U13/2+V13/4,0)</f>
         <v>7</v>
       </c>
-      <c r="X13" s="5" t="n">
+      <c r="X13" s="6" t="n">
         <f aca="false">ROUND(W13*10/$AA$1,0)</f>
         <v>8</v>
       </c>
-      <c r="Y13" s="0" t="s">
+      <c r="Y13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Z13" s="3" t="n">
+      <c r="Z13" s="4" t="n">
         <v>0.541666666666667</v>
       </c>
-      <c r="AA13" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC13" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD13" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF13" s="0" t="s">
+      <c r="AA13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AG13" s="3" t="n">
+      <c r="AG13" s="4" t="n">
         <v>0.527777777777778</v>
       </c>
-      <c r="AH13" s="0" t="s">
+      <c r="AH13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI13" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="0" t="s">
+      <c r="E14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" s="4" t="n">
         <v>0.527777777777778</v>
       </c>
-      <c r="K14" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="L14" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="M14" s="0" t="s">
+      <c r="K14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N14" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="P14" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q14" s="0" t="s">
+      <c r="N14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" s="4" t="n">
         <v>0.513888888888889</v>
       </c>
-      <c r="S14" s="4" t="n">
+      <c r="S14" s="1" t="n">
         <f aca="false">COUNTIF(E14:Q14,"E")</f>
         <v>0</v>
       </c>
-      <c r="T14" s="0" t="n">
+      <c r="T14" s="1" t="n">
         <f aca="false">COUNTIF(E14:Q14,"P")</f>
         <v>7</v>
       </c>
-      <c r="U14" s="0" t="n">
+      <c r="U14" s="1" t="n">
         <f aca="false">COUNTIF(E14:Q14,"M")</f>
         <v>2</v>
       </c>
-      <c r="V14" s="0" t="n">
+      <c r="V14" s="1" t="n">
         <f aca="false">COUNTIF(E14:Q14,"T")</f>
         <v>0</v>
       </c>
-      <c r="W14" s="0" t="n">
+      <c r="W14" s="1" t="n">
         <f aca="false">ROUND(T14+U14/2+V14/4,0)</f>
         <v>8</v>
       </c>
-      <c r="X14" s="5" t="n">
+      <c r="X14" s="6" t="n">
         <f aca="false">ROUND(W14*10/$AA$1,0)</f>
         <v>9</v>
       </c>
-      <c r="Y14" s="0" t="s">
+      <c r="Y14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AA14" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC14" s="0" t="s">
+      <c r="AA14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AD14" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF14" s="0" t="s">
+      <c r="AD14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH14" s="0" t="s">
+      <c r="AH14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI14" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="0" t="s">
+      <c r="E15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="4" t="n">
         <v>0.527777777777778</v>
       </c>
-      <c r="H15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="L15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="N15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="P15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="S15" s="4" t="n">
+      <c r="H15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S15" s="1" t="n">
         <f aca="false">COUNTIF(E15:Q15,"E")</f>
         <v>0</v>
       </c>
-      <c r="T15" s="0" t="n">
+      <c r="T15" s="1" t="n">
         <f aca="false">COUNTIF(E15:Q15,"P")</f>
         <v>8</v>
       </c>
-      <c r="U15" s="0" t="n">
+      <c r="U15" s="1" t="n">
         <f aca="false">COUNTIF(E15:Q15,"M")</f>
         <v>1</v>
       </c>
-      <c r="V15" s="0" t="n">
+      <c r="V15" s="1" t="n">
         <f aca="false">COUNTIF(E15:Q15,"T")</f>
         <v>0</v>
       </c>
-      <c r="W15" s="0" t="n">
+      <c r="W15" s="1" t="n">
         <f aca="false">ROUND(T15+U15/2+V15/4,0)</f>
         <v>9</v>
       </c>
-      <c r="X15" s="5" t="n">
+      <c r="X15" s="6" t="n">
         <f aca="false">ROUND(W15*10/$AA$1,0)</f>
         <v>10</v>
       </c>
-      <c r="Y15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH15" s="0" t="s">
+      <c r="Y15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI15" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="0" t="s">
+      <c r="E16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="4" t="n">
         <v>0.53125</v>
       </c>
-      <c r="H16" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="0" t="s">
+      <c r="H16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K16" s="0" t="s">
+      <c r="K16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L16" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="N16" s="0" t="s">
+      <c r="L16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P16" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q16" s="0" t="s">
+      <c r="P16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="4" t="n">
         <v>0.534722222222222</v>
       </c>
-      <c r="S16" s="4" t="n">
+      <c r="S16" s="1" t="n">
         <f aca="false">COUNTIF(E16:Q16,"E")</f>
         <v>0</v>
       </c>
-      <c r="T16" s="0" t="n">
+      <c r="T16" s="1" t="n">
         <f aca="false">COUNTIF(E16:Q16,"P")</f>
         <v>4</v>
       </c>
-      <c r="U16" s="0" t="n">
+      <c r="U16" s="1" t="n">
         <f aca="false">COUNTIF(E16:Q16,"M")</f>
         <v>1</v>
       </c>
-      <c r="V16" s="0" t="n">
+      <c r="V16" s="1" t="n">
         <f aca="false">COUNTIF(E16:Q16,"T")</f>
         <v>1</v>
       </c>
-      <c r="W16" s="0" t="n">
+      <c r="W16" s="1" t="n">
         <f aca="false">ROUND(T16+U16/2+V16/4,0)</f>
         <v>5</v>
       </c>
-      <c r="X16" s="5" t="n">
+      <c r="X16" s="6" t="n">
         <f aca="false">ROUND(W16*10/$AA$1,0)</f>
         <v>6</v>
       </c>
-      <c r="Y16" s="0" t="s">
+      <c r="Y16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AA16" s="0" t="s">
+      <c r="AA16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AC16" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD16" s="0" t="s">
+      <c r="AC16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AF16" s="0" t="s">
+      <c r="AF16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AG16" s="3" t="n">
+      <c r="AG16" s="4" t="n">
         <v>0.527777777777778</v>
       </c>
-      <c r="AH16" s="0" t="s">
-        <v>15</v>
+      <c r="AH16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI16" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="0" t="s">
+      <c r="H17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="0" t="s">
+      <c r="I17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="0" t="s">
+      <c r="K17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="0" t="s">
+      <c r="L17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N17" s="0" t="s">
+      <c r="N17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P17" s="0" t="s">
+      <c r="P17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q17" s="0" t="s">
+      <c r="Q17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="S17" s="4" t="n">
+      <c r="S17" s="1" t="n">
         <f aca="false">COUNTIF(E17:Q17,"E")</f>
         <v>0</v>
       </c>
-      <c r="T17" s="0" t="n">
+      <c r="T17" s="1" t="n">
         <f aca="false">COUNTIF(E17:Q17,"P")</f>
         <v>0</v>
       </c>
-      <c r="U17" s="0" t="n">
+      <c r="U17" s="1" t="n">
         <f aca="false">COUNTIF(E17:Q17,"M")</f>
         <v>0</v>
       </c>
-      <c r="V17" s="0" t="n">
+      <c r="V17" s="1" t="n">
         <f aca="false">COUNTIF(E17:Q17,"T")</f>
         <v>0</v>
       </c>
-      <c r="W17" s="0" t="n">
+      <c r="W17" s="1" t="n">
         <f aca="false">ROUND(T17+U17/2+V17/4,0)</f>
         <v>0</v>
       </c>
-      <c r="X17" s="5" t="n">
+      <c r="X17" s="6" t="n">
         <f aca="false">ROUND(W17*10/$AA$1,0)</f>
         <v>0</v>
       </c>
-      <c r="Y17" s="0" t="s">
+      <c r="Y17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AA17" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC17" s="0" t="s">
+      <c r="AA17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AD17" s="0" t="s">
+      <c r="AD17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AF17" s="0" t="s">
+      <c r="AF17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH17" s="0" t="s">
+      <c r="AH17" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="AI17" s="7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="N18" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="P18" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q18" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="S18" s="4" t="n">
+      <c r="E18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S18" s="1" t="n">
         <f aca="false">COUNTIF(E18:Q18,"E")</f>
         <v>0</v>
       </c>
-      <c r="T18" s="0" t="n">
+      <c r="T18" s="1" t="n">
         <f aca="false">COUNTIF(E18:Q18,"P")</f>
         <v>9</v>
       </c>
-      <c r="U18" s="0" t="n">
+      <c r="U18" s="1" t="n">
         <f aca="false">COUNTIF(E18:Q18,"M")</f>
         <v>0</v>
       </c>
-      <c r="V18" s="0" t="n">
+      <c r="V18" s="1" t="n">
         <f aca="false">COUNTIF(E18:Q18,"T")</f>
         <v>0</v>
       </c>
-      <c r="W18" s="0" t="n">
+      <c r="W18" s="1" t="n">
         <f aca="false">ROUND(T18+U18/2+V18/4,0)</f>
         <v>9</v>
       </c>
-      <c r="X18" s="5" t="n">
+      <c r="X18" s="6" t="n">
         <f aca="false">ROUND(W18*10/$AA$1,0)</f>
         <v>10</v>
       </c>
-      <c r="Y18" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA18" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC18" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD18" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF18" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH18" s="0" t="s">
+      <c r="Y18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI18" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="1" t="n">
         <f aca="false">COUNTIF(E3:E18,"P")</f>
         <v>14</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="F19" s="1" t="n">
         <f aca="false">COUNTIF(F3:F18,"P")</f>
         <v>13</v>
       </c>
-      <c r="H19" s="0" t="n">
+      <c r="H19" s="1" t="n">
         <f aca="false">COUNTIF(H3:H18,"P")</f>
         <v>13</v>
       </c>
-      <c r="I19" s="0" t="n">
+      <c r="I19" s="1" t="n">
         <f aca="false">COUNTIF(I3:I18,"P")</f>
         <v>11</v>
       </c>
-      <c r="K19" s="0" t="n">
+      <c r="K19" s="1" t="n">
         <f aca="false">COUNTIF(K3:K18,"P")</f>
         <v>14</v>
       </c>
-      <c r="L19" s="0" t="n">
+      <c r="L19" s="1" t="n">
         <f aca="false">COUNTIF(L3:L18,"P")</f>
         <v>14</v>
       </c>
-      <c r="N19" s="0" t="n">
+      <c r="N19" s="1" t="n">
         <f aca="false">COUNTIF(N3:N18,"P")</f>
         <v>11</v>
       </c>
-      <c r="P19" s="0" t="n">
+      <c r="P19" s="1" t="n">
         <f aca="false">COUNTIF(P3:P18,"P")</f>
         <v>15</v>
       </c>
-      <c r="Q19" s="0" t="n">
+      <c r="Q19" s="1" t="n">
         <f aca="false">COUNTIF(Q3:Q18,"P")</f>
         <v>11</v>
       </c>
-      <c r="Y19" s="0" t="n">
+      <c r="Y19" s="1" t="n">
         <f aca="false">COUNTIF(Y3:Y18,"P")</f>
         <v>9</v>
       </c>
-      <c r="AA19" s="0" t="n">
+      <c r="AA19" s="1" t="n">
         <f aca="false">COUNTIF(AA3:AA18,"P")</f>
         <v>12</v>
       </c>
-      <c r="AC19" s="0" t="n">
+      <c r="AC19" s="1" t="n">
         <f aca="false">COUNTIF(AC3:AC18,"P")</f>
         <v>14</v>
       </c>
-      <c r="AD19" s="0" t="n">
+      <c r="AD19" s="1" t="n">
         <f aca="false">COUNTIF(AD3:AD18,"P")</f>
         <v>13</v>
       </c>
-      <c r="AF19" s="0" t="n">
+      <c r="AF19" s="1" t="n">
         <f aca="false">COUNTIF(AF3:AF18,"P")</f>
         <v>10</v>
       </c>
-      <c r="AH19" s="0" t="n">
+      <c r="AH19" s="1" t="n">
         <f aca="false">COUNTIF(AH3:AH18,"P")</f>
         <v>15</v>
       </c>
+      <c r="AI19" s="1" t="n">
+        <f aca="false">COUNTIF(AI3:AI18,"P")</f>
+        <v>13</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="1" t="n">
         <f aca="false">COUNTIF(E3:E18,"M")</f>
         <v>0</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="F20" s="1" t="n">
         <f aca="false">COUNTIF(F3:F18,"M")</f>
         <v>2</v>
       </c>
-      <c r="I20" s="0" t="n">
+      <c r="I20" s="1" t="n">
         <f aca="false">COUNTIF(I3:I18,"M")</f>
         <v>1</v>
       </c>
-      <c r="Y20" s="0" t="n">
+      <c r="Y20" s="1" t="n">
         <f aca="false">COUNTIF(Y3:Y18,"M")</f>
         <v>2</v>
       </c>
-      <c r="AA20" s="0" t="n">
+      <c r="AA20" s="1" t="n">
         <f aca="false">COUNTIF(AA3:AA18,"M")</f>
         <v>1</v>
       </c>
-      <c r="AC20" s="0" t="n">
+      <c r="AC20" s="1" t="n">
         <f aca="false">COUNTIF(AC3:AC18,"M")</f>
         <v>0</v>
       </c>
-      <c r="AD20" s="0" t="n">
+      <c r="AD20" s="1" t="n">
         <f aca="false">COUNTIF(AD3:AD18,"M")</f>
         <v>0</v>
       </c>
-      <c r="AF20" s="0" t="n">
+      <c r="AF20" s="1" t="n">
         <f aca="false">COUNTIF(AF3:AF18,"M")</f>
         <v>0</v>
       </c>
-      <c r="AH20" s="0" t="n">
+      <c r="AH20" s="1" t="n">
         <f aca="false">COUNTIF(AH3:AH18,"M")</f>
         <v>0</v>
       </c>
+      <c r="AI20" s="1" t="n">
+        <f aca="false">COUNTIF(AI3:AI18,"M")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21" s="1" t="n">
         <f aca="false">COUNTIF(E3:E18,"T")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="F21" s="1" t="n">
         <f aca="false">COUNTIF(F3:F18,"T")</f>
         <v>0</v>
       </c>
-      <c r="I21" s="0" t="n">
+      <c r="I21" s="1" t="n">
         <f aca="false">COUNTIF(I3:I18,"T")</f>
         <v>1</v>
       </c>
-      <c r="Y21" s="0" t="n">
+      <c r="Y21" s="1" t="n">
         <f aca="false">COUNTIF(Y3:Y18,"T")</f>
         <v>1</v>
       </c>
-      <c r="AA21" s="0" t="n">
+      <c r="AA21" s="1" t="n">
         <f aca="false">COUNTIF(AA3:AA18,"T")</f>
         <v>1</v>
       </c>
-      <c r="AC21" s="0" t="n">
+      <c r="AC21" s="1" t="n">
         <f aca="false">COUNTIF(AC3:AC18,"T")</f>
         <v>0</v>
       </c>
-      <c r="AD21" s="0" t="n">
+      <c r="AD21" s="1" t="n">
         <f aca="false">COUNTIF(AD3:AD18,"T")</f>
         <v>1</v>
       </c>
-      <c r="AE21" s="3" t="n">
+      <c r="AE21" s="4" t="n">
         <v>0.611111111111111</v>
       </c>
-      <c r="AF21" s="0" t="n">
+      <c r="AF21" s="1" t="n">
         <f aca="false">COUNTIF(AF3:AF18,"T")</f>
         <v>2</v>
       </c>
-      <c r="AH21" s="0" t="n">
+      <c r="AH21" s="1" t="n">
         <f aca="false">COUNTIF(AH3:AH18,"T")</f>
         <v>0</v>
       </c>
+      <c r="AI21" s="1" t="n">
+        <f aca="false">COUNTIF(AI3:AI18,"T")</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="0" t="n">
+      <c r="C22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="1" t="n">
         <f aca="false">SUM(Y19:Y21)</f>
         <v>12</v>
       </c>
-      <c r="AA22" s="0" t="n">
+      <c r="AA22" s="1" t="n">
         <f aca="false">SUM(AA19:AA21)</f>
         <v>14</v>
       </c>
-      <c r="AC22" s="0" t="n">
+      <c r="AC22" s="1" t="n">
         <f aca="false">SUM(AC19:AC21)</f>
         <v>14</v>
       </c>
-      <c r="AD22" s="0" t="n">
+      <c r="AD22" s="1" t="n">
         <f aca="false">SUM(AD19:AD21)</f>
         <v>14</v>
       </c>
-      <c r="AF22" s="0" t="n">
+      <c r="AF22" s="1" t="n">
         <f aca="false">SUM(AF19:AF21)</f>
         <v>12</v>
       </c>
-      <c r="AH22" s="0" t="n">
+      <c r="AH22" s="1" t="n">
         <f aca="false">SUM(AH19:AH21)</f>
         <v>15</v>
+      </c>
+      <c r="AI22" s="1" t="n">
+        <f aca="false">SUM(AI19:AI21)</f>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2819,1056 +3012,1056 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA17"/>
   <sheetFormatPr defaultColWidth="9.62109375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.21"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="3" style="0" width="9.37"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="18" min="15" style="0" width="9.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="24.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.21"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="3" style="1" width="9.37"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="18" min="15" style="1" width="9.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="24.87"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="R1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="S1" s="0" t="s">
+      <c r="S1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="T1" s="2" t="n">
+      <c r="T1" s="3" t="n">
         <v>45876</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="V1" s="0" t="s">
+      <c r="V1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="W1" s="0" t="s">
+      <c r="W1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="X1" s="0" t="s">
+      <c r="X1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="Y1" s="0" t="s">
+      <c r="Y1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="Z1" s="0" t="s">
+      <c r="Z1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AA1" s="0" t="s">
+      <c r="AA1" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="0" t="n">
+      <c r="C2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1" t="n">
         <f aca="false">ROUND(K2+M2/2,0)</f>
         <v>2</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="O2" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C2,E2,G2,I2,N2),0)</f>
         <v>1</v>
       </c>
-      <c r="P2" s="4" t="str">
+      <c r="P2" s="1" t="str">
         <f aca="false">IF(O2&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="Q2" s="0" t="n">
+      <c r="Q2" s="1" t="n">
         <v>1.4</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="R2" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="S2" s="4" t="n">
+      <c r="S2" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q2:R2,O2),0)</f>
         <v>3</v>
       </c>
-      <c r="T2" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y2" s="0" t="n">
+      <c r="T2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y2" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="Z2" s="0" t="s">
+      <c r="Z2" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>45782</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E3" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>45782</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>45782</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I3" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="3" t="n">
         <v>45782</v>
       </c>
-      <c r="K3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="0" t="n">
+      <c r="K3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1" t="n">
         <f aca="false">ROUND(K3+M3/2,0)</f>
         <v>2</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C3,E3,G3,I3,N3),0)</f>
         <v>6</v>
       </c>
-      <c r="P3" s="4" t="str">
+      <c r="P3" s="1" t="str">
         <f aca="false">IF(O3&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="Q3" s="0" t="n">
+      <c r="Q3" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="R3" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="S3" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q3:R3,O3),0)</f>
         <v>6</v>
       </c>
-      <c r="T3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y3" s="0" t="n">
+      <c r="T3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Z3" s="0" t="s">
+      <c r="Z3" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>8.7</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <f aca="false">ROUND(MAX(G4,E4),0)</f>
         <v>9</v>
       </c>
-      <c r="K4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="8" t="n">
+      <c r="K4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="1" t="n">
         <f aca="false">ROUND(K4+M4/2,0)</f>
         <v>8</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="O4" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C4,E4,G4,I4,N4),0)</f>
         <v>9</v>
       </c>
-      <c r="P4" s="4" t="str">
+      <c r="P4" s="1" t="str">
         <f aca="false">IF(O4&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q4" s="0" t="n">
+      <c r="Q4" s="1" t="n">
         <v>9.3</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="R4" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="S4" s="4" t="n">
+      <c r="S4" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q4:R4,O4),0)</f>
         <v>9</v>
       </c>
-      <c r="V4" s="0" t="s">
+      <c r="V4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="W4" s="0" t="n">
+      <c r="W4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Y4" s="0" t="n">
+      <c r="Y4" s="1" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <f aca="false">ROUND(K5+M5/2,0)</f>
         <v>10</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="O5" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C5,E5,G5,I5,N5),0)</f>
         <v>8</v>
       </c>
-      <c r="P5" s="4" t="str">
+      <c r="P5" s="1" t="str">
         <f aca="false">IF(O5&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q5" s="0" t="n">
+      <c r="Q5" s="1" t="n">
         <v>4.4</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="R5" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="S5" s="4" t="n">
+      <c r="S5" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q5:R5,O5),0)</f>
         <v>7</v>
       </c>
-      <c r="V5" s="0" t="s">
+      <c r="V5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="W5" s="0" t="n">
+      <c r="W5" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Y5" s="0" t="n">
+      <c r="Y5" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Z5" s="0" t="s">
+      <c r="Z5" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <f aca="false">ROUND(K6+M6/2,0)</f>
         <v>9</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="O6" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C6,E6,G6,I6,N6),0)</f>
         <v>7</v>
       </c>
-      <c r="P6" s="4" t="str">
+      <c r="P6" s="1" t="str">
         <f aca="false">IF(O6&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q6" s="0" t="n">
+      <c r="Q6" s="1" t="n">
         <v>4.2</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="R6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="S6" s="4" t="n">
+      <c r="S6" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q6:R6,O6),0)</f>
         <v>7</v>
       </c>
-      <c r="V6" s="0" t="s">
+      <c r="V6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="W6" s="0" t="n">
+      <c r="W6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Y6" s="0" t="n">
+      <c r="Y6" s="1" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="8" t="n">
+      <c r="C7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="13" t="n">
         <v>45848</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="13" t="n">
         <v>45849</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="13" t="n">
         <v>45849</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="M7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="0" t="n">
+      <c r="M7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <f aca="false">ROUND(K7+M7/2,0)</f>
         <v>2</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="O7" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C7,E7,G7,I7,N7),0)</f>
         <v>3</v>
       </c>
-      <c r="P7" s="4" t="str">
+      <c r="P7" s="1" t="str">
         <f aca="false">IF(O7&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="Q7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="6" t="n">
+      <c r="Q7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="S7" s="4" t="n">
+      <c r="S7" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q7:R7,O7),0)</f>
         <v>4</v>
       </c>
-      <c r="T7" s="0" t="s">
+      <c r="T7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y7" s="0" t="n">
+      <c r="Y7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="Z7" s="0" t="s">
+      <c r="Z7" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+    <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="13" t="n">
         <v>45848</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H8" s="13" t="n">
         <v>45849</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="J8" s="9" t="n">
+      <c r="J8" s="13" t="n">
         <v>45849</v>
       </c>
-      <c r="K8" s="8" t="n">
+      <c r="K8" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="13" t="n">
         <v>45849</v>
       </c>
-      <c r="M8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="0" t="n">
+      <c r="M8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <f aca="false">ROUND(K8+M8/2,0)</f>
         <v>5</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="O8" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C8,E8,G8,I8,N8),0)</f>
         <v>5</v>
       </c>
-      <c r="P8" s="4" t="str">
+      <c r="P8" s="1" t="str">
         <f aca="false">IF(O8&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="Q8" s="0" t="n">
+      <c r="Q8" s="1" t="n">
         <v>0.8</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="R8" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="S8" s="4" t="n">
+      <c r="S8" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q8:R8,O8),0)</f>
         <v>5</v>
       </c>
-      <c r="T8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y8" s="0" t="n">
+      <c r="T8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y8" s="1" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="13" t="n">
         <v>45855</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="K9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="0" t="n">
+      <c r="K9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1" t="n">
         <f aca="false">ROUND(K9+M9/2,0)</f>
         <v>1</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="O9" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C9,E9,G9,I9,N9),0)</f>
         <v>6</v>
       </c>
-      <c r="P9" s="4" t="str">
+      <c r="P9" s="1" t="str">
         <f aca="false">IF(O9&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="Q9" s="0" t="n">
+      <c r="Q9" s="1" t="n">
         <v>1.6</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="R9" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="S9" s="4" t="n">
+      <c r="S9" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q9:R9,O9),0)</f>
         <v>6</v>
       </c>
-      <c r="T9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y9" s="0" t="n">
+      <c r="T9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y9" s="1" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <v>45782</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" s="3" t="n">
         <v>45774</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="K10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="1" t="n">
         <f aca="false">ROUND(K10+M10/2,0)</f>
         <v>14</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="O10" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C10,E10,G10,I10,N10),0)</f>
         <v>9</v>
       </c>
-      <c r="P10" s="4" t="str">
+      <c r="P10" s="1" t="str">
         <f aca="false">IF(O10&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q10" s="0" t="n">
+      <c r="Q10" s="1" t="n">
         <v>8.6</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="R10" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="S10" s="4" t="n">
+      <c r="S10" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q10:R10,O10),0)</f>
         <v>9</v>
       </c>
-      <c r="Y10" s="0" t="n">
+      <c r="Y10" s="1" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="13" t="n">
         <v>45849</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <f aca="false">ROUND(MAX(G12,E12),0)</f>
         <v>8</v>
       </c>
-      <c r="K11" s="8" t="n">
+      <c r="K11" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" s="13" t="n">
         <v>45849</v>
       </c>
-      <c r="M11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="0" t="n">
+      <c r="M11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1" t="n">
         <f aca="false">ROUND(K11+M11/2,0)</f>
         <v>8</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="O11" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C11,E11,G11,I11,N11),0)</f>
         <v>8</v>
       </c>
-      <c r="P11" s="4" t="str">
+      <c r="P11" s="1" t="str">
         <f aca="false">IF(O11&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q11" s="0" t="n">
+      <c r="Q11" s="1" t="n">
         <v>2.1</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="R11" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="S11" s="4" t="n">
+      <c r="S11" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q11:R11,O11),0)</f>
         <v>7</v>
       </c>
-      <c r="Y11" s="0" t="n">
+      <c r="Y11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Z11" s="0" t="s">
+      <c r="Z11" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="8" t="n">
+      <c r="C12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H12" s="13" t="n">
         <v>45849</v>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="I12" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="9" t="n">
+      <c r="J12" s="13" t="n">
         <v>45849</v>
       </c>
-      <c r="K12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="0" t="n">
+      <c r="K12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="1" t="n">
         <f aca="false">ROUND(K12+M12/2,0)</f>
         <v>3</v>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="O12" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C12,E12,G12,I12,N12),0)</f>
         <v>3</v>
       </c>
-      <c r="P12" s="4" t="str">
+      <c r="P12" s="1" t="str">
         <f aca="false">IF(O12&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="Q12" s="0" t="n">
+      <c r="Q12" s="1" t="n">
         <v>2.8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="R12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="S12" s="4" t="n">
+      <c r="S12" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q12:R12,O12),0)</f>
         <v>5</v>
       </c>
-      <c r="T12" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y12" s="0" t="n">
+      <c r="T12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y12" s="1" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="0" t="n">
+      <c r="E13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I13" s="0" t="n">
+      <c r="I13" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="K13" s="0" t="n">
+      <c r="K13" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="M13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="0" t="n">
+      <c r="M13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1" t="n">
         <f aca="false">ROUND(K13+M13/2,0)</f>
         <v>6</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="O13" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C13,E13,G13,I13,N13),0)</f>
         <v>5</v>
       </c>
-      <c r="P13" s="4" t="str">
+      <c r="P13" s="1" t="str">
         <f aca="false">IF(O13&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="Q13" s="0" t="n">
+      <c r="Q13" s="1" t="n">
         <v>2.4</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="R13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="S13" s="4" t="n">
+      <c r="S13" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q13:R13,O13),0)</f>
         <v>5</v>
       </c>
-      <c r="T13" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y13" s="0" t="n">
+      <c r="T13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y13" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z13" s="0" t="s">
+      <c r="Z13" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="0" t="n">
+      <c r="C14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1" t="n">
         <f aca="false">ROUND(K14+M14/2,0)</f>
         <v>2</v>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="O14" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C14,E14,G14,I14,N14),0)</f>
         <v>1</v>
       </c>
-      <c r="P14" s="4" t="str">
+      <c r="P14" s="1" t="str">
         <f aca="false">IF(O14&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="Q14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" s="6" t="n">
+      <c r="Q14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="S14" s="4" t="n">
+      <c r="S14" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q14:R14,O14),0)</f>
         <v>4</v>
       </c>
-      <c r="T14" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y14" s="0" t="n">
+      <c r="T14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y14" s="1" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="0" t="n">
+      <c r="E15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1" t="n">
         <f aca="false">ROUND(K15+M15/2,0)</f>
         <v>1</v>
       </c>
-      <c r="O15" s="4" t="n">
+      <c r="O15" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C15,E15,G15,I15,N15),0)</f>
         <v>2</v>
       </c>
-      <c r="P15" s="4" t="str">
+      <c r="P15" s="1" t="str">
         <f aca="false">IF(O15&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="Q15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" s="6" t="n">
+      <c r="Q15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="S15" s="4" t="n">
+      <c r="S15" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q15:R15,O15),0)</f>
         <v>3</v>
       </c>
-      <c r="T15" s="0" t="s">
+      <c r="T15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="V15" s="0" t="s">
+      <c r="V15" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="W15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="0" t="s">
+      <c r="W15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
+    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="0" t="n">
+      <c r="C16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="N16" s="1" t="n">
         <f aca="false">ROUND(K16+M16/2,0)</f>
         <v>2</v>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="O16" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C16,E16,G16,I16,N16),0)</f>
         <v>1</v>
       </c>
-      <c r="P16" s="4" t="str">
+      <c r="P16" s="1" t="str">
         <f aca="false">IF(O16&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="Q16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="4" t="n">
+      <c r="Q16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q16:R16,O16),0)</f>
         <v>1</v>
       </c>
-      <c r="T16" s="0" t="s">
+      <c r="T16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y16" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="Y16" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I17" s="0" t="n">
+      <c r="I17" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="K17" s="0" t="n">
+      <c r="K17" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="M17" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N17" s="1" t="n">
         <f aca="false">ROUND(K17+M17/2,0)</f>
         <v>7</v>
       </c>
-      <c r="O17" s="4" t="n">
+      <c r="O17" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C17,E17,G17,I17,N17),0)</f>
         <v>8</v>
       </c>
-      <c r="P17" s="4" t="str">
+      <c r="P17" s="1" t="str">
         <f aca="false">IF(O17&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q17" s="0" t="n">
+      <c r="Q17" s="1" t="n">
         <v>1.8</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="R17" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="S17" s="4" t="n">
+      <c r="S17" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(Q17:R17,O17),0)</f>
         <v>7</v>
       </c>
-      <c r="V17" s="0" t="s">
+      <c r="V17" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="W17" s="0" t="n">
+      <c r="W17" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Y17" s="0" t="n">
+      <c r="Y17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="Z17" s="0" t="s">
+      <c r="Z17" s="1" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3896,504 +4089,504 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="9.62109375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.23"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="0" t="n">
+      <c r="F2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="0" t="n">
+      <c r="F3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <f aca="false">AVERAGE(F6:F8)</f>
         <v>5.33333333333333</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="1" t="n">
         <f aca="false">ROUND(MAX(H6,G6),0)</f>
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="0" t="n">
+      <c r="F9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <f aca="false">AVERAGE(F10:F11)</f>
         <v>5.5</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <f aca="false">ROUND(MAX(H10,G10),0)</f>
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <f aca="false">AVERAGE(F12:F16)</f>
         <v>4.8</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="I12" s="1" t="n">
         <f aca="false">ROUND(MAX(H12,G12),0)</f>
         <v>5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I17" s="0" t="n">
+      <c r="I17" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I18" s="0" t="n">
+      <c r="I18" s="1" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="0" t="n">
+      <c r="F19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="F20" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I20" s="0" t="n">
+      <c r="I20" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="0" t="n">
+      <c r="F21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F22" s="0" t="n">
+      <c r="F22" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I22" s="0" t="n">
+      <c r="I22" s="1" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="A23" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="0" t="n">
+      <c r="F23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="F24" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="G24" s="1" t="n">
         <f aca="false">AVERAGE(F24:F25)</f>
         <v>8.5</v>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="H24" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I24" s="0" t="n">
+      <c r="I24" s="1" t="n">
         <f aca="false">ROUND(MAX(H24,G24),0)</f>
         <v>9</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F25" s="0" t="n">
+      <c r="F25" s="1" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4409,534 +4602,534 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultColWidth="9.62109375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.51"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="0" t="n">
+      <c r="F2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="0" t="n">
+      <c r="F3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>8.7</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <v>8.7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>5.8</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <f aca="false">AVERAGE(F5:F6)</f>
         <v>4.35</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="1" t="n">
         <f aca="false">ROUND(MAX(H5,G5),0)</f>
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>2.9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>6.9</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="0" t="n">
+      <c r="F8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>5.9</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <f aca="false">AVERAGE(F9:F11)</f>
         <v>2.93333333333333</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <f aca="false">ROUND(MAX(H9,G9),0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>2.8</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <f aca="false">AVERAGE(F12:F13)</f>
         <v>1.85</v>
       </c>
-      <c r="H12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="0" t="n">
+      <c r="H12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="n">
         <f aca="false">ROUND(MAX(H12,G12),0)</f>
         <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="I14" s="0" t="n">
+      <c r="I14" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <v>7.8</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="G15" s="1" t="n">
         <f aca="false">AVERAGE(F15:F16)</f>
         <v>6.75</v>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="H15" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I15" s="0" t="n">
+      <c r="I15" s="1" t="n">
         <f aca="false">ROUND(MAX(H15,G15),0)</f>
         <v>7</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="1" t="n">
         <v>5.7</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="0" t="n">
+      <c r="F17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="0" t="n">
+      <c r="F18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="0" t="n">
+      <c r="F19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="0" t="n">
+      <c r="F20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="A21" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="0" t="n">
+      <c r="F21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F22" s="0" t="n">
+      <c r="F22" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="G22" s="0" t="n">
+      <c r="G22" s="1" t="n">
         <f aca="false">AVERAGE(F22:F27)</f>
         <v>5.78333333333333</v>
       </c>
-      <c r="H22" s="0" t="n">
+      <c r="H22" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I22" s="0" t="n">
+      <c r="I22" s="1" t="n">
         <f aca="false">ROUND(MAX(H22,G22),0)</f>
         <v>9</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F23" s="0" t="n">
+      <c r="F23" s="1" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="F24" s="1" t="n">
         <v>6.9</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F25" s="0" t="n">
+      <c r="F25" s="1" t="n">
         <v>4.9</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="E26" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F26" s="0" t="n">
+      <c r="F26" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E27" s="0" t="s">
+      <c r="E27" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="F27" s="1" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -4952,483 +5145,483 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="9.62109375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.51"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="0" t="n">
+      <c r="F2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="0" t="n">
+      <c r="F3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <f aca="false">AVERAGE(F4:F5)</f>
         <v>9</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <f aca="false">ROUND(MAX(H4,G4),0)</f>
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="1" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <f aca="false">AVERAGE(F7:F8)</f>
         <v>7</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <f aca="false">ROUND(MAX(H7,G7),0)</f>
         <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="0" t="n">
+      <c r="F9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <f aca="false">AVERAGE(F11:F12)</f>
         <v>9.5</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <f aca="false">ROUND(MAX(H11,G11),0)</f>
         <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I13" s="0" t="n">
+      <c r="I13" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14" s="1" t="n">
         <f aca="false">AVERAGE(F14:F18)</f>
         <v>4</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="0" t="n">
+      <c r="I14" s="1" t="n">
         <f aca="false">ROUND(MAX(H14,G14),0)</f>
         <v>4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="0" t="n">
+      <c r="F19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="F20" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I20" s="0" t="n">
+      <c r="I20" s="1" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="0" t="n">
+      <c r="F21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="0" t="n">
+      <c r="F22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="A23" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="0" t="n">
+      <c r="F23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="F24" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I24" s="0" t="n">
+      <c r="I24" s="1" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5444,426 +5637,426 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="9.62109375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="0" t="n">
+      <c r="F2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="0" t="n">
+      <c r="F3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <f aca="false">AVERAGE(F4:F5)</f>
         <v>8.5</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <f aca="false">ROUND(MAX(H4,G4),0)</f>
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="0" t="n">
+      <c r="F8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="F11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="0" t="n">
+      <c r="F11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <f aca="false">AVERAGE(F12:F15)</f>
         <v>4</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="I12" s="1" t="n">
         <f aca="false">ROUND(MAX(H12,G12),0)</f>
         <v>4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="0" t="n">
+      <c r="F16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I17" s="0" t="n">
+      <c r="I17" s="1" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="0" t="n">
+      <c r="F18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="0" t="n">
+      <c r="F19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="A20" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="0" t="n">
+      <c r="F20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="F21" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I21" s="0" t="n">
+      <c r="I21" s="1" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5879,380 +6072,380 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="9.62109375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.51"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="0" t="n">
+      <c r="F2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="0" t="n">
+      <c r="F3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="0" t="n">
+      <c r="F4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="0" t="n">
+      <c r="F9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="I10" s="1" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <f aca="false">AVERAGE(F11:F12)</f>
         <v>3</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="I11" s="1" t="n">
         <f aca="false">ROUND(MAX(H11,G11),0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="0" t="n">
+      <c r="F13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I14" s="0" t="n">
+      <c r="I14" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="0" t="n">
+      <c r="F15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="0" t="n">
+      <c r="F16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="0" t="n">
+      <c r="F17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I18" s="0" t="n">
+      <c r="I18" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="1"/>
+      <c r="B25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="1"/>
+      <c r="B26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="1"/>
+      <c r="B27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="1"/>
+      <c r="B28" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6266,346 +6459,346 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O17"/>
   <sheetFormatPr defaultColWidth="9.62109375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.21"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="n">
+      <c r="C1" s="3" t="n">
         <v>45736</v>
       </c>
-      <c r="D1" s="2" t="n">
+      <c r="D1" s="3" t="n">
         <v>45750</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="2" t="n">
+      <c r="F1" s="3" t="n">
         <v>45799</v>
       </c>
-      <c r="G1" s="2" t="n">
+      <c r="G1" s="3" t="n">
         <v>45806</v>
       </c>
-      <c r="H1" s="2" t="n">
+      <c r="H1" s="3" t="n">
         <v>45813</v>
       </c>
-      <c r="I1" s="2" t="n">
+      <c r="I1" s="3" t="n">
         <v>45820</v>
       </c>
-      <c r="J1" s="2" t="n">
+      <c r="J1" s="3" t="n">
         <v>45827</v>
       </c>
-      <c r="K1" s="2" t="n">
+      <c r="K1" s="3" t="n">
         <v>45834</v>
       </c>
-      <c r="L1" s="2" t="n">
+      <c r="L1" s="3" t="n">
         <v>45841</v>
       </c>
-      <c r="M1" s="2" t="n">
+      <c r="M1" s="3" t="n">
         <v>45848</v>
       </c>
-      <c r="N1" s="2" t="n">
+      <c r="N1" s="3" t="n">
         <v>45855</v>
       </c>
-      <c r="O1" s="2"/>
+      <c r="O1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="0" t="n">
+      <c r="C2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <f aca="false">C2+D2</f>
         <v>1</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="0" t="n">
+      <c r="C3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <f aca="false">C3+D3</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <f aca="false">C4+D4</f>
         <v>8</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="n">
+      <c r="C5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <f aca="false">C5+D5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <f aca="false">C6+D6</f>
         <v>6</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="0" t="n">
+      <c r="C7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="n">
         <f aca="false">C7+D7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="0" t="n">
+      <c r="C8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="n">
         <f aca="false">C8+D8</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="0" t="n">
+      <c r="C9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="n">
         <f aca="false">C9+D9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <f aca="false">C10+D10</f>
         <v>4</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10" s="1" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="0" t="n">
+      <c r="C11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="n">
         <f aca="false">C11+D11</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="0" t="n">
+      <c r="C12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <f aca="false">C12+D12</f>
         <v>3</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="0" t="n">
+      <c r="C13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1" t="n">
         <f aca="false">C13+D13</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="0" t="n">
+      <c r="C14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="n">
         <f aca="false">C14+D14</f>
         <v>0</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="L14" s="0" t="n">
+      <c r="L14" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="0" t="n">
+      <c r="C15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="n">
         <f aca="false">C15+D15</f>
         <v>0</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="1" t="n">
         <f aca="false">C16+D16</f>
         <v>2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <f aca="false">C17+D17</f>
         <v>2</v>
       </c>
@@ -6622,323 +6815,323 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="9.4453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.44921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="17.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="17.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.2"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>9.3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>4.4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>4.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>1.6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>8.6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>2.1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>2.8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <v>2.4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F16" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <v>1.8</v>
       </c>
     </row>

--- a/inasistencias-4b-tc/alumnos-4b-tc.xlsx
+++ b/inasistencias-4b-tc/alumnos-4b-tc.xlsx
@@ -1068,7 +1068,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1090,10 +1090,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1121,39 +1117,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1308,7 +1276,6 @@
           <bgColor rgb="FFCCFFCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -1323,7 +1290,6 @@
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -1339,7 +1305,6 @@
           <bgColor rgb="FFCC0000"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
   </dxfs>
   <colors>
@@ -1561,13 +1526,13 @@
       <c r="AY1" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AZ1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="BC1" s="0" t="n">
+      <c r="AZ1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC1" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="BD1" s="0" t="n">
+      <c r="BD1" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1695,13 +1660,13 @@
       <c r="AO2" s="4" t="n">
         <v>45974</v>
       </c>
-      <c r="AP2" s="7" t="n">
+      <c r="AP2" s="6" t="n">
         <v>45981</v>
       </c>
-      <c r="AQ2" s="7" t="n">
+      <c r="AQ2" s="6" t="n">
         <v>45988</v>
       </c>
-      <c r="AR2" s="8" t="s">
+      <c r="AR2" s="7" t="s">
         <v>6</v>
       </c>
       <c r="AS2" s="1" t="s">
@@ -1725,33 +1690,33 @@
       <c r="AY2" s="4" t="n">
         <v>46002</v>
       </c>
-      <c r="AZ2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="BA2" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="BB2" s="9" t="s">
+      <c r="AZ2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="BA2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="BB2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="BC2" s="6" t="s">
+      <c r="BC2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="BD2" s="6" t="s">
+      <c r="BD2" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -1787,7 +1752,7 @@
       <c r="Q3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="R3" s="10" t="n">
+      <c r="R3" s="9" t="n">
         <v>0.541666666666667</v>
       </c>
       <c r="S3" s="2" t="n">
@@ -1810,20 +1775,20 @@
         <f aca="false">ROUND(T3+U3/2+V3/4,0)</f>
         <v>7</v>
       </c>
-      <c r="X3" s="11" t="n">
+      <c r="X3" s="10" t="n">
         <f aca="false">ROUND(W3*10/$AA$1,0)</f>
         <v>8</v>
       </c>
       <c r="Y3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z3" s="10" t="n">
+      <c r="Z3" s="9" t="n">
         <v>0.520833333333333</v>
       </c>
       <c r="AA3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AB3" s="10" t="n">
+      <c r="AB3" s="9" t="n">
         <v>0.527777777777778</v>
       </c>
       <c r="AC3" s="2" t="s">
@@ -1840,23 +1805,23 @@
       <c r="AH3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AI3" s="9" t="s">
+      <c r="AI3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="AJ3" s="10" t="n">
+      <c r="AJ3" s="9" t="n">
         <v>0.538194444444444</v>
       </c>
-      <c r="AK3" s="9" t="s">
+      <c r="AK3" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AL3" s="2"/>
       <c r="AM3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AN3" s="10" t="n">
+      <c r="AN3" s="9" t="n">
         <v>0.597222222222222</v>
       </c>
-      <c r="AO3" s="9" t="s">
+      <c r="AO3" s="8" t="s">
         <v>26</v>
       </c>
       <c r="AP3" s="2" t="s">
@@ -1865,7 +1830,7 @@
       <c r="AQ3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AR3" s="10" t="n">
+      <c r="AR3" s="9" t="n">
         <v>0.520833333333333</v>
       </c>
       <c r="AS3" s="2" t="n">
@@ -1880,40 +1845,40 @@
         <f aca="false">COUNTIF(Y3:AO3,"T")</f>
         <v>3</v>
       </c>
-      <c r="AV3" s="12" t="n">
+      <c r="AV3" s="11" t="n">
         <f aca="false">ROUND(AS3+AT3/2+AU3/4,0)</f>
         <v>6</v>
       </c>
-      <c r="AW3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AY3" s="9" t="s">
+      <c r="AW3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AZ3" s="13" t="n">
+      <c r="AZ3" s="2" t="n">
         <f aca="false">COUNTIF(AW3:AY3,"P")</f>
         <v>1</v>
       </c>
-      <c r="BA3" s="13" t="n">
+      <c r="BA3" s="2" t="n">
         <f aca="false">COUNTIF(AW3:AY3,"T")</f>
         <v>0</v>
       </c>
-      <c r="BB3" s="13" t="n">
+      <c r="BB3" s="2" t="n">
         <f aca="false">ROUND((AZ3+BA3/2)*5,0)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="4" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -1968,14 +1933,14 @@
         <f aca="false">ROUND(T4+U4/2+V4/4,0)</f>
         <v>7</v>
       </c>
-      <c r="X4" s="11" t="n">
+      <c r="X4" s="10" t="n">
         <f aca="false">ROUND(W4*10/$AA$1,0)</f>
         <v>8</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z4" s="10" t="n">
+      <c r="Z4" s="9" t="n">
         <v>0.513888888888889</v>
       </c>
       <c r="AA4" s="2" t="s">
@@ -1996,11 +1961,11 @@
       <c r="AH4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AI4" s="9" t="s">
+      <c r="AI4" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AJ4" s="2"/>
-      <c r="AK4" s="9" t="s">
+      <c r="AK4" s="8" t="s">
         <v>26</v>
       </c>
       <c r="AL4" s="2"/>
@@ -2008,7 +1973,7 @@
         <v>21</v>
       </c>
       <c r="AN4" s="2"/>
-      <c r="AO4" s="9" t="s">
+      <c r="AO4" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AP4" s="2" t="s">
@@ -2030,25 +1995,25 @@
         <f aca="false">COUNTIF(Y4:AO4,"T")</f>
         <v>0</v>
       </c>
-      <c r="AV4" s="12" t="n">
+      <c r="AV4" s="11" t="n">
         <f aca="false">ROUND(AS4+AT4/2+AU4/4,0)</f>
         <v>8</v>
       </c>
-      <c r="AW4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AY4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ4" s="13" t="n">
+      <c r="AW4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ4" s="2" t="n">
         <f aca="false">COUNTIF(AW4:AY4,"P")</f>
         <v>2</v>
       </c>
-      <c r="BA4" s="13" t="n">
+      <c r="BA4" s="2" t="n">
         <f aca="false">COUNTIF(AW4:AY4,"T")</f>
         <v>0</v>
       </c>
-      <c r="BB4" s="13" t="n">
+      <c r="BB4" s="2" t="n">
         <f aca="false">ROUND((AZ4+BA4/2)*5,0)</f>
         <v>10</v>
       </c>
@@ -2113,7 +2078,7 @@
         <f aca="false">ROUND(T5+U5/2+V5/4,0)</f>
         <v>9</v>
       </c>
-      <c r="X5" s="14" t="n">
+      <c r="X5" s="12" t="n">
         <f aca="false">ROUND(W5*10/$AA$1,0)</f>
         <v>10</v>
       </c>
@@ -2165,7 +2130,7 @@
         <f aca="false">COUNTIF(Y5:AO5,"T")</f>
         <v>0</v>
       </c>
-      <c r="AV5" s="15" t="n">
+      <c r="AV5" s="13" t="n">
         <f aca="false">ROUND(AS5+AT5/2+AU5/4,0)</f>
         <v>10</v>
       </c>
@@ -2233,7 +2198,7 @@
         <f aca="false">ROUND(T6+U6/2+V6/4,0)</f>
         <v>8</v>
       </c>
-      <c r="X6" s="14" t="n">
+      <c r="X6" s="12" t="n">
         <f aca="false">ROUND(W6*10/$AA$1,0)</f>
         <v>9</v>
       </c>
@@ -2285,7 +2250,7 @@
         <f aca="false">COUNTIF(Y6:AO6,"T")</f>
         <v>0</v>
       </c>
-      <c r="AV6" s="15" t="n">
+      <c r="AV6" s="13" t="n">
         <f aca="false">ROUND(AS6+AT6/2+AU6/4,0)</f>
         <v>9</v>
       </c>
@@ -2350,7 +2315,7 @@
         <f aca="false">ROUND(T7+U7/2+V7/4,0)</f>
         <v>9</v>
       </c>
-      <c r="X7" s="14" t="n">
+      <c r="X7" s="12" t="n">
         <f aca="false">ROUND(W7*10/$AA$1,0)</f>
         <v>10</v>
       </c>
@@ -2402,22 +2367,22 @@
         <f aca="false">COUNTIF(Y7:AO7,"T")</f>
         <v>0</v>
       </c>
-      <c r="AV7" s="15" t="n">
+      <c r="AV7" s="13" t="n">
         <f aca="false">ROUND(AS7+AT7/2+AU7/4,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="8" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -2472,7 +2437,7 @@
         <f aca="false">ROUND(T8+U8/2+V8/4,0)</f>
         <v>8</v>
       </c>
-      <c r="X8" s="11" t="n">
+      <c r="X8" s="10" t="n">
         <f aca="false">ROUND(W8*10/$AA$1,0)</f>
         <v>9</v>
       </c>
@@ -2498,11 +2463,11 @@
       <c r="AH8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AI8" s="9" t="s">
+      <c r="AI8" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AJ8" s="2"/>
-      <c r="AK8" s="9" t="s">
+      <c r="AK8" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AL8" s="2"/>
@@ -2510,7 +2475,7 @@
         <v>21</v>
       </c>
       <c r="AN8" s="2"/>
-      <c r="AO8" s="9" t="s">
+      <c r="AO8" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AP8" s="2" t="s">
@@ -2532,40 +2497,40 @@
         <f aca="false">COUNTIF(Y8:AO8,"T")</f>
         <v>0</v>
       </c>
-      <c r="AV8" s="12" t="n">
+      <c r="AV8" s="11" t="n">
         <f aca="false">ROUND(AS8+AT8/2+AU8/4,0)</f>
         <v>10</v>
       </c>
-      <c r="AW8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AY8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ8" s="13" t="n">
+      <c r="AW8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ8" s="2" t="n">
         <f aca="false">COUNTIF(AW8:AY8,"P")</f>
         <v>2</v>
       </c>
-      <c r="BA8" s="13" t="n">
+      <c r="BA8" s="2" t="n">
         <f aca="false">COUNTIF(AW8:AY8,"T")</f>
         <v>0</v>
       </c>
-      <c r="BB8" s="13" t="n">
+      <c r="BB8" s="2" t="n">
         <f aca="false">ROUND((AZ8+BA8/2)*5,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="9" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -2622,7 +2587,7 @@
         <f aca="false">ROUND(T9+U9/2+V9/4,0)</f>
         <v>7</v>
       </c>
-      <c r="X9" s="11" t="n">
+      <c r="X9" s="10" t="n">
         <f aca="false">ROUND(W9*10/$AA$1,0)</f>
         <v>8</v>
       </c>
@@ -2633,7 +2598,7 @@
       <c r="AA9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB9" s="10" t="n">
+      <c r="AB9" s="9" t="n">
         <v>0.520833333333333</v>
       </c>
       <c r="AC9" s="2" t="s">
@@ -2650,21 +2615,21 @@
       <c r="AH9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AI9" s="9" t="s">
+      <c r="AI9" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AJ9" s="2"/>
-      <c r="AK9" s="9" t="s">
+      <c r="AK9" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AL9" s="2"/>
       <c r="AM9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AN9" s="10" t="n">
+      <c r="AN9" s="9" t="n">
         <v>0.541666666666667</v>
       </c>
-      <c r="AO9" s="9" t="s">
+      <c r="AO9" s="8" t="s">
         <v>26</v>
       </c>
       <c r="AP9" s="2" t="s">
@@ -2686,40 +2651,40 @@
         <f aca="false">COUNTIF(Y9:AO9,"T")</f>
         <v>1</v>
       </c>
-      <c r="AV9" s="12" t="n">
+      <c r="AV9" s="11" t="n">
         <f aca="false">ROUND(AS9+AT9/2+AU9/4,0)</f>
         <v>8</v>
       </c>
-      <c r="AW9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AY9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ9" s="13" t="n">
+      <c r="AW9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ9" s="2" t="n">
         <f aca="false">COUNTIF(AW9:AY9,"P")</f>
         <v>2</v>
       </c>
-      <c r="BA9" s="13" t="n">
+      <c r="BA9" s="2" t="n">
         <f aca="false">COUNTIF(AW9:AY9,"T")</f>
         <v>0</v>
       </c>
-      <c r="BB9" s="13" t="n">
+      <c r="BB9" s="2" t="n">
         <f aca="false">ROUND((AZ9+BA9/2)*5,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="10" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -2774,7 +2739,7 @@
         <f aca="false">ROUND(T10+U10/2+V10/4,0)</f>
         <v>8</v>
       </c>
-      <c r="X10" s="11" t="n">
+      <c r="X10" s="10" t="n">
         <f aca="false">ROUND(W10*10/$AA$1,0)</f>
         <v>9</v>
       </c>
@@ -2800,11 +2765,11 @@
       <c r="AH10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AI10" s="9" t="s">
+      <c r="AI10" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AJ10" s="2"/>
-      <c r="AK10" s="9" t="s">
+      <c r="AK10" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AL10" s="2"/>
@@ -2812,7 +2777,7 @@
         <v>21</v>
       </c>
       <c r="AN10" s="2"/>
-      <c r="AO10" s="9" t="s">
+      <c r="AO10" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AP10" s="2" t="s">
@@ -2834,25 +2799,25 @@
         <f aca="false">COUNTIF(Y10:AO10,"T")</f>
         <v>0</v>
       </c>
-      <c r="AV10" s="12" t="n">
+      <c r="AV10" s="11" t="n">
         <f aca="false">ROUND(AS10+AT10/2+AU10/4,0)</f>
         <v>8</v>
       </c>
-      <c r="AW10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AY10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ10" s="13" t="n">
+      <c r="AW10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ10" s="2" t="n">
         <f aca="false">COUNTIF(AW10:AY10,"P")</f>
         <v>2</v>
       </c>
-      <c r="BA10" s="13" t="n">
+      <c r="BA10" s="2" t="n">
         <f aca="false">COUNTIF(AW10:AY10,"T")</f>
         <v>0</v>
       </c>
-      <c r="BB10" s="13" t="n">
+      <c r="BB10" s="2" t="n">
         <f aca="false">ROUND((AZ10+BA10/2)*5,0)</f>
         <v>10</v>
       </c>
@@ -2917,7 +2882,7 @@
         <f aca="false">ROUND(T11+U11/2+V11/4,0)</f>
         <v>9</v>
       </c>
-      <c r="X11" s="14" t="n">
+      <c r="X11" s="12" t="n">
         <f aca="false">ROUND(W11*10/$AA$1,0)</f>
         <v>10</v>
       </c>
@@ -2969,7 +2934,7 @@
         <f aca="false">COUNTIF(Y11:AO11,"T")</f>
         <v>0</v>
       </c>
-      <c r="AV11" s="15" t="n">
+      <c r="AV11" s="13" t="n">
         <f aca="false">ROUND(AS11+AT11/2+AU11/4,0)</f>
         <v>8</v>
       </c>
@@ -3034,7 +2999,7 @@
         <f aca="false">ROUND(T12+U12/2+V12/4,0)</f>
         <v>9</v>
       </c>
-      <c r="X12" s="14" t="n">
+      <c r="X12" s="12" t="n">
         <f aca="false">ROUND(W12*10/$AA$1,0)</f>
         <v>10</v>
       </c>
@@ -3086,7 +3051,7 @@
         <f aca="false">COUNTIF(Y12:AO12,"T")</f>
         <v>0</v>
       </c>
-      <c r="AV12" s="15" t="n">
+      <c r="AV12" s="13" t="n">
         <f aca="false">ROUND(AS12+AT12/2+AU12/4,0)</f>
         <v>10</v>
       </c>
@@ -3154,7 +3119,7 @@
         <f aca="false">ROUND(T13+U13/2+V13/4,0)</f>
         <v>7</v>
       </c>
-      <c r="X13" s="14" t="n">
+      <c r="X13" s="12" t="n">
         <f aca="false">ROUND(W13*10/$AA$1,0)</f>
         <v>8</v>
       </c>
@@ -3212,22 +3177,22 @@
         <f aca="false">COUNTIF(Y13:AO13,"T")</f>
         <v>2</v>
       </c>
-      <c r="AV13" s="15" t="n">
+      <c r="AV13" s="13" t="n">
         <f aca="false">ROUND(AS13+AT13/2+AU13/4,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="8" t="s">
         <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -3243,7 +3208,7 @@
       <c r="I14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J14" s="10" t="n">
+      <c r="J14" s="9" t="n">
         <v>0.527777777777778</v>
       </c>
       <c r="K14" s="2" t="s">
@@ -3265,7 +3230,7 @@
       <c r="Q14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="R14" s="10" t="n">
+      <c r="R14" s="9" t="n">
         <v>0.513888888888889</v>
       </c>
       <c r="S14" s="2" t="n">
@@ -3288,7 +3253,7 @@
         <f aca="false">ROUND(T14+U14/2+V14/4,0)</f>
         <v>8</v>
       </c>
-      <c r="X14" s="11" t="n">
+      <c r="X14" s="10" t="n">
         <f aca="false">ROUND(W14*10/$AA$1,0)</f>
         <v>9</v>
       </c>
@@ -3314,23 +3279,23 @@
       <c r="AH14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AI14" s="9" t="s">
+      <c r="AI14" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AJ14" s="2"/>
-      <c r="AK14" s="9" t="s">
+      <c r="AK14" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AL14" s="10" t="n">
+      <c r="AL14" s="9" t="n">
         <v>0.513888888888889</v>
       </c>
       <c r="AM14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AN14" s="10" t="n">
+      <c r="AN14" s="9" t="n">
         <v>0.527777777777778</v>
       </c>
-      <c r="AO14" s="9" t="s">
+      <c r="AO14" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AP14" s="2" t="s">
@@ -3352,43 +3317,43 @@
         <f aca="false">COUNTIF(Y14:AO14,"T")</f>
         <v>1</v>
       </c>
-      <c r="AV14" s="12" t="n">
+      <c r="AV14" s="11" t="n">
         <f aca="false">ROUND(AS14+AT14/2+AU14/4,0)</f>
         <v>6</v>
       </c>
-      <c r="AW14" s="9" t="s">
+      <c r="AW14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="AX14" s="10" t="n">
+      <c r="AX14" s="9" t="n">
         <v>0.53125</v>
       </c>
-      <c r="AY14" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ14" s="13" t="n">
+      <c r="AY14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ14" s="2" t="n">
         <f aca="false">COUNTIF(AW14:AY14,"P")</f>
         <v>1</v>
       </c>
-      <c r="BA14" s="13" t="n">
+      <c r="BA14" s="2" t="n">
         <f aca="false">COUNTIF(AW14:AY14,"T")</f>
         <v>1</v>
       </c>
-      <c r="BB14" s="13" t="n">
+      <c r="BB14" s="2" t="n">
         <f aca="false">ROUND((AZ14+BA14/2)*5,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="15" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="8" t="s">
         <v>65</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -3397,7 +3362,7 @@
       <c r="F15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="G15" s="9" t="n">
         <v>0.527777777777778</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -3445,7 +3410,7 @@
         <f aca="false">ROUND(T15+U15/2+V15/4,0)</f>
         <v>9</v>
       </c>
-      <c r="X15" s="11" t="n">
+      <c r="X15" s="10" t="n">
         <f aca="false">ROUND(W15*10/$AA$1,0)</f>
         <v>10</v>
       </c>
@@ -3471,11 +3436,11 @@
       <c r="AH15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AI15" s="9" t="s">
+      <c r="AI15" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AJ15" s="2"/>
-      <c r="AK15" s="9" t="s">
+      <c r="AK15" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AL15" s="2"/>
@@ -3483,7 +3448,7 @@
         <v>21</v>
       </c>
       <c r="AN15" s="2"/>
-      <c r="AO15" s="9" t="s">
+      <c r="AO15" s="8" t="s">
         <v>21</v>
       </c>
       <c r="AP15" s="2" t="s">
@@ -3505,40 +3470,40 @@
         <f aca="false">COUNTIF(Y15:AO15,"T")</f>
         <v>0</v>
       </c>
-      <c r="AV15" s="12" t="n">
+      <c r="AV15" s="11" t="n">
         <f aca="false">ROUND(AS15+AT15/2+AU15/4,0)</f>
         <v>10</v>
       </c>
-      <c r="AW15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AY15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ15" s="13" t="n">
+      <c r="AW15" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY15" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ15" s="2" t="n">
         <f aca="false">COUNTIF(AW15:AY15,"P")</f>
         <v>2</v>
       </c>
-      <c r="BA15" s="13" t="n">
+      <c r="BA15" s="2" t="n">
         <f aca="false">COUNTIF(AW15:AY15,"T")</f>
         <v>0</v>
       </c>
-      <c r="BB15" s="13" t="n">
+      <c r="BB15" s="2" t="n">
         <f aca="false">ROUND((AZ15+BA15/2)*5,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="16" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="8" t="s">
         <v>68</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -3547,7 +3512,7 @@
       <c r="F16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="G16" s="9" t="n">
         <v>0.53125</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -3574,7 +3539,7 @@
       <c r="Q16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="R16" s="9" t="n">
         <v>0.534722222222222</v>
       </c>
       <c r="S16" s="2" t="n">
@@ -3597,7 +3562,7 @@
         <f aca="false">ROUND(T16+U16/2+V16/4,0)</f>
         <v>5</v>
       </c>
-      <c r="X16" s="11" t="n">
+      <c r="X16" s="10" t="n">
         <f aca="false">ROUND(W16*10/$AA$1,0)</f>
         <v>6</v>
       </c>
@@ -3619,17 +3584,17 @@
       <c r="AF16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AG16" s="10" t="n">
+      <c r="AG16" s="9" t="n">
         <v>0.527777777777778</v>
       </c>
       <c r="AH16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AI16" s="9" t="s">
+      <c r="AI16" s="8" t="s">
         <v>26</v>
       </c>
       <c r="AJ16" s="2"/>
-      <c r="AK16" s="9" t="s">
+      <c r="AK16" s="8" t="s">
         <v>26</v>
       </c>
       <c r="AL16" s="2"/>
@@ -3637,7 +3602,7 @@
         <v>26</v>
       </c>
       <c r="AN16" s="2"/>
-      <c r="AO16" s="9" t="s">
+      <c r="AO16" s="8" t="s">
         <v>26</v>
       </c>
       <c r="AP16" s="2" t="s">
@@ -3659,43 +3624,43 @@
         <f aca="false">COUNTIF(Y16:AO16,"T")</f>
         <v>2</v>
       </c>
-      <c r="AV16" s="12" t="n">
+      <c r="AV16" s="11" t="n">
         <f aca="false">ROUND(AS16+AT16/2+AU16/4,0)</f>
         <v>3</v>
       </c>
-      <c r="AW16" s="9" t="s">
+      <c r="AW16" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="AX16" s="10" t="n">
+      <c r="AX16" s="9" t="n">
         <v>0.597222222222222</v>
       </c>
-      <c r="AY16" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ16" s="13" t="n">
+      <c r="AY16" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ16" s="2" t="n">
         <f aca="false">COUNTIF(AW16:AY16,"P")</f>
         <v>1</v>
       </c>
-      <c r="BA16" s="13" t="n">
+      <c r="BA16" s="2" t="n">
         <f aca="false">COUNTIF(AW16:AY16,"T")</f>
         <v>1</v>
       </c>
-      <c r="BB16" s="13" t="n">
+      <c r="BB16" s="2" t="n">
         <f aca="false">ROUND((AZ16+BA16/2)*5,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="17" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -3750,7 +3715,7 @@
         <f aca="false">ROUND(T17+U17/2+V17/4,0)</f>
         <v>0</v>
       </c>
-      <c r="X17" s="11" t="n">
+      <c r="X17" s="10" t="n">
         <f aca="false">ROUND(W17*10/$AA$1,0)</f>
         <v>0</v>
       </c>
@@ -3776,11 +3741,11 @@
       <c r="AH17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AI17" s="9" t="s">
+      <c r="AI17" s="8" t="s">
         <v>26</v>
       </c>
       <c r="AJ17" s="2"/>
-      <c r="AK17" s="9" t="s">
+      <c r="AK17" s="8" t="s">
         <v>26</v>
       </c>
       <c r="AL17" s="2"/>
@@ -3788,7 +3753,7 @@
         <v>26</v>
       </c>
       <c r="AN17" s="2"/>
-      <c r="AO17" s="9" t="s">
+      <c r="AO17" s="8" t="s">
         <v>26</v>
       </c>
       <c r="AP17" s="2" t="s">
@@ -3810,25 +3775,25 @@
         <f aca="false">COUNTIF(Y17:AO17,"T")</f>
         <v>0</v>
       </c>
-      <c r="AV17" s="12" t="n">
+      <c r="AV17" s="11" t="n">
         <f aca="false">ROUND(AS17+AT17/2+AU17/4,0)</f>
         <v>1</v>
       </c>
-      <c r="AW17" s="9" t="s">
+      <c r="AW17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AY17" s="9" t="s">
+      <c r="AY17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AZ17" s="13" t="n">
+      <c r="AZ17" s="2" t="n">
         <f aca="false">COUNTIF(AW17:AY17,"P")</f>
         <v>0</v>
       </c>
-      <c r="BA17" s="13" t="n">
+      <c r="BA17" s="2" t="n">
         <f aca="false">COUNTIF(AW17:AY17,"T")</f>
         <v>0</v>
       </c>
-      <c r="BB17" s="13" t="n">
+      <c r="BB17" s="2" t="n">
         <f aca="false">ROUND((AZ17+BA17/2)*5,0)</f>
         <v>0</v>
       </c>
@@ -3893,7 +3858,7 @@
         <f aca="false">ROUND(T18+U18/2+V18/4,0)</f>
         <v>9</v>
       </c>
-      <c r="X18" s="14" t="n">
+      <c r="X18" s="12" t="n">
         <f aca="false">ROUND(W18*10/$AA$1,0)</f>
         <v>10</v>
       </c>
@@ -3945,7 +3910,7 @@
         <f aca="false">COUNTIF(Y18:AO18,"T")</f>
         <v>0</v>
       </c>
-      <c r="AV18" s="15" t="n">
+      <c r="AV18" s="13" t="n">
         <f aca="false">ROUND(AS18+AT18/2+AU18/4,0)</f>
         <v>10</v>
       </c>
@@ -4615,13 +4580,11 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.21"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="3" style="1" width="9.37"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="18" min="15" style="1" width="9.58"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="19" min="19" style="0" width="9.62"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="25" min="20" style="1" width="9.62"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="1" width="24.87"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="32" min="27" style="1" width="9.62"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="35" min="33" style="0" width="9.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="1" width="9.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="15" style="1" width="9.58"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="25" min="19" style="1" width="9.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="24.87"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="35" min="27" style="1" width="9.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4640,7 +4603,6 @@
       <c r="AG1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AH1" s="1"/>
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
     </row>
@@ -4753,1604 +4715,1584 @@
       <c r="AJ2" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="AK2" s="6" t="s">
+      <c r="AK2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" s="16" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="17" t="s">
+    <row r="3" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="D3" s="18" t="n">
+      <c r="C3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>45995</v>
       </c>
-      <c r="E3" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="16" t="n">
+      <c r="E3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1" t="n">
         <f aca="false">ROUND(K3+M3/2,0)</f>
         <v>2</v>
       </c>
-      <c r="O3" s="16" t="n">
+      <c r="O3" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C3,E3,G3,I3,N3),0)</f>
         <v>3</v>
       </c>
-      <c r="P3" s="16" t="str">
+      <c r="P3" s="1" t="str">
         <f aca="false">IF(O3&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="Q3" s="16" t="n">
+      <c r="Q3" s="1" t="n">
         <v>1.4</v>
       </c>
-      <c r="R3" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="S3" s="20" t="n">
+      <c r="R3" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="S3" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q3:R3,O3),0)</f>
         <v>4</v>
       </c>
-      <c r="T3" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="U3" s="16" t="n">
+      <c r="T3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="U3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="V3" s="17" t="s">
+      <c r="V3" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="W3" s="16" t="n">
+      <c r="W3" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="X3" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="16" t="n">
+      <c r="X3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="Z3" s="16" t="s">
+      <c r="Z3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="AA3" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB3" s="16" t="n">
+      <c r="AA3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB3" s="1" t="n">
         <f aca="false">Y3+AA3/2</f>
         <v>10</v>
       </c>
-      <c r="AC3" s="16" t="n">
+      <c r="AC3" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AD3" s="20" t="n">
+      <c r="AD3" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U3,W3,X3,AB3,AC3),0)</f>
         <v>5</v>
       </c>
-      <c r="AE3" s="20" t="n">
+      <c r="AE3" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S3,AD3),0)</f>
         <v>5</v>
       </c>
-      <c r="AF3" s="20" t="n">
+      <c r="AF3" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="AG3" s="20" t="n">
+      <c r="AG3" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(C3,E3,G3,I3,K3),0)</f>
         <v>2</v>
       </c>
-      <c r="AH3" s="20" t="n">
+      <c r="AH3" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U3,AF3),0)</f>
         <v>4</v>
       </c>
-      <c r="AI3" s="20" t="n">
+      <c r="AI3" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(AG3,AH3),0)</f>
         <v>3</v>
       </c>
-      <c r="AJ3" s="16" t="n">
+      <c r="AJ3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AK3" s="16" t="s">
+      <c r="AK3" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="4" s="16" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="n">
+    <row r="4" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="4" t="n">
         <v>45782</v>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" s="18" t="n">
+      <c r="E4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>45995</v>
       </c>
-      <c r="G4" s="16" t="n">
+      <c r="G4" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="4" t="n">
         <v>45782</v>
       </c>
-      <c r="I4" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="J4" s="18" t="n">
+      <c r="I4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" s="4" t="n">
         <v>45782</v>
       </c>
-      <c r="K4" s="16" t="n">
+      <c r="K4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="M4" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="16" t="n">
+      <c r="M4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1" t="n">
         <f aca="false">ROUND(K4+M4/2,0)</f>
         <v>6</v>
       </c>
-      <c r="O4" s="16" t="n">
+      <c r="O4" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C4,E4,G4,I4,N4),0)</f>
         <v>8</v>
       </c>
-      <c r="P4" s="16" t="str">
+      <c r="P4" s="1" t="str">
         <f aca="false">IF(O4&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q4" s="16" t="n">
+      <c r="Q4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="R4" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="S4" s="20" t="n">
+      <c r="R4" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="S4" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q4:R4,O4),0)</f>
         <v>6</v>
       </c>
-      <c r="T4" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="U4" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="17" t="s">
+      <c r="T4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="W4" s="16" t="n">
+      <c r="W4" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="X4" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="16" t="n">
+      <c r="X4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Z4" s="16" t="s">
+      <c r="Z4" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="AA4" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB4" s="16" t="n">
+      <c r="AA4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB4" s="1" t="n">
         <f aca="false">Y4+AA4/2</f>
         <v>7</v>
       </c>
-      <c r="AC4" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD4" s="20" t="n">
+      <c r="AC4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD4" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U4,W4,X4,AB4,AC4),0)</f>
         <v>5</v>
       </c>
-      <c r="AE4" s="20" t="n">
+      <c r="AE4" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S4,AD4),0)</f>
         <v>6</v>
       </c>
-      <c r="AF4" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG4" s="20" t="n">
+      <c r="AF4" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG4" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(C4,E4,G4,I4,K4),0)</f>
         <v>8</v>
       </c>
-      <c r="AH4" s="20" t="n">
+      <c r="AH4" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U4,AF4),0)</f>
         <v>6</v>
       </c>
-      <c r="AI4" s="20" t="n">
+      <c r="AI4" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(AG4,AH4),0)</f>
         <v>7</v>
       </c>
-      <c r="AJ4" s="16" t="n">
+      <c r="AJ4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AK4" s="16" t="s">
+      <c r="AK4" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="5" s="21" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="n">
+    <row r="5" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16" t="n">
+      <c r="C5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>8.7</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16" t="n">
+      <c r="I5" s="1" t="n">
         <f aca="false">ROUND(MAX(G5,E5),0)</f>
         <v>9</v>
       </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16" t="n">
+      <c r="K5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="N5" s="16" t="n">
+      <c r="N5" s="1" t="n">
         <f aca="false">ROUND(K5+M5/2,0)</f>
         <v>8</v>
       </c>
-      <c r="O5" s="16" t="n">
+      <c r="O5" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C5,E5,G5,I5,N5),0)</f>
         <v>9</v>
       </c>
-      <c r="P5" s="16" t="str">
+      <c r="P5" s="1" t="str">
         <f aca="false">IF(O5&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q5" s="16" t="n">
+      <c r="Q5" s="1" t="n">
         <v>9.3</v>
       </c>
-      <c r="R5" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="S5" s="20" t="n">
+      <c r="R5" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S5" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q5:R5,O5),0)</f>
         <v>9</v>
       </c>
-      <c r="T5" s="16"/>
-      <c r="U5" s="16" t="n">
+      <c r="U5" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V5" s="16" t="s">
+      <c r="V5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="W5" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="X5" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y5" s="16" t="n">
+      <c r="W5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y5" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z5" s="16"/>
-      <c r="AA5" s="16" t="n">
+      <c r="AA5" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="AB5" s="16" t="n">
+      <c r="AB5" s="1" t="n">
         <f aca="false">Y5+AA5/2</f>
         <v>14.5</v>
       </c>
-      <c r="AC5" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD5" s="20" t="n">
+      <c r="AC5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD5" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U5,W5,X5,AB5,AC5),0)</f>
         <v>11</v>
       </c>
-      <c r="AE5" s="20" t="n">
+      <c r="AE5" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S5,AD5),0)</f>
         <v>10</v>
       </c>
-      <c r="AF5" s="20"/>
-      <c r="AG5" s="20"/>
-      <c r="AI5" s="20"/>
-    </row>
-    <row r="6" s="21" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="n">
+      <c r="AF5" s="13"/>
+      <c r="AG5" s="13"/>
+      <c r="AH5" s="13"/>
+      <c r="AI5" s="13"/>
+    </row>
+    <row r="6" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="n">
+      <c r="C6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16" t="n">
+      <c r="I6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16" t="n">
+      <c r="K6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16" t="n">
+      <c r="M6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="N6" s="16" t="n">
+      <c r="N6" s="1" t="n">
         <f aca="false">ROUND(K6+M6/2,0)</f>
         <v>10</v>
       </c>
-      <c r="O6" s="16" t="n">
+      <c r="O6" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C6,E6,G6,I6,N6),0)</f>
         <v>8</v>
       </c>
-      <c r="P6" s="16" t="str">
+      <c r="P6" s="1" t="str">
         <f aca="false">IF(O6&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q6" s="16" t="n">
+      <c r="Q6" s="1" t="n">
         <v>4.4</v>
       </c>
-      <c r="R6" s="19" t="n">
+      <c r="R6" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="S6" s="20" t="n">
+      <c r="S6" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q6:R6,O6),0)</f>
         <v>7</v>
       </c>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16" t="n">
+      <c r="U6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="V6" s="16" t="s">
+      <c r="V6" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="W6" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="X6" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y6" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z6" s="16" t="s">
+      <c r="W6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z6" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA6" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB6" s="16" t="n">
+      <c r="AA6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB6" s="1" t="n">
         <f aca="false">Y6+AA6/2</f>
         <v>15</v>
       </c>
-      <c r="AC6" s="16" t="n">
+      <c r="AC6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AD6" s="20" t="n">
+      <c r="AD6" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U6,W6,X6,AB6,AC6),0)</f>
         <v>10</v>
       </c>
-      <c r="AE6" s="20" t="n">
+      <c r="AE6" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S6,AD6),0)</f>
         <v>9</v>
       </c>
-      <c r="AF6" s="20"/>
-      <c r="AG6" s="20"/>
-      <c r="AI6" s="20"/>
-    </row>
-    <row r="7" s="21" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="n">
+      <c r="AF6" s="13"/>
+      <c r="AG6" s="13"/>
+      <c r="AH6" s="13"/>
+      <c r="AI6" s="13"/>
+    </row>
+    <row r="7" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16" t="n">
+      <c r="I7" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16" t="n">
+      <c r="K7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="N7" s="16" t="n">
+      <c r="M7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <f aca="false">ROUND(K7+M7/2,0)</f>
         <v>9</v>
       </c>
-      <c r="O7" s="16" t="n">
+      <c r="O7" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C7,E7,G7,I7,N7),0)</f>
         <v>7</v>
       </c>
-      <c r="P7" s="16" t="str">
+      <c r="P7" s="1" t="str">
         <f aca="false">IF(O7&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q7" s="16" t="n">
+      <c r="Q7" s="1" t="n">
         <v>4.2</v>
       </c>
-      <c r="R7" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="S7" s="20" t="n">
+      <c r="R7" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S7" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q7:R7,O7),0)</f>
         <v>7</v>
       </c>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16" t="n">
+      <c r="U7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="V7" s="16" t="s">
+      <c r="V7" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="W7" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="X7" s="16" t="n">
+      <c r="W7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="X7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="Y7" s="16" t="n">
+      <c r="Y7" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB7" s="16" t="n">
+      <c r="AA7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB7" s="1" t="n">
         <f aca="false">Y7+AA7/2</f>
         <v>14</v>
       </c>
-      <c r="AC7" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD7" s="20" t="n">
+      <c r="AC7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD7" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U7,W7,X7,AB7,AC7),0)</f>
         <v>9</v>
       </c>
-      <c r="AE7" s="20" t="n">
+      <c r="AE7" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S7,AD7),0)</f>
         <v>8</v>
       </c>
-      <c r="AF7" s="20"/>
-      <c r="AG7" s="20"/>
-      <c r="AI7" s="20"/>
-    </row>
-    <row r="8" s="16" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="n">
+      <c r="AF7" s="13"/>
+      <c r="AG7" s="13"/>
+      <c r="AH7" s="13"/>
+      <c r="AI7" s="13"/>
+    </row>
+    <row r="8" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" s="18" t="n">
+      <c r="C8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>45988</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="4" t="n">
         <v>46002</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="H8" s="4" t="n">
         <v>45849</v>
       </c>
-      <c r="I8" s="16" t="n">
+      <c r="I8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="4" t="n">
         <v>45849</v>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="K8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="16" t="n">
+      <c r="M8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <f aca="false">ROUND(K8+M8/2,0)</f>
         <v>7</v>
       </c>
-      <c r="O8" s="16" t="n">
+      <c r="O8" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C8,E8,G8,I8,N8),0)</f>
         <v>6</v>
       </c>
-      <c r="P8" s="16" t="str">
+      <c r="P8" s="1" t="str">
         <f aca="false">IF(O8&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="Q8" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" s="19" t="n">
+      <c r="Q8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="S8" s="20" t="n">
+      <c r="S8" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q8:R8,O8),0)</f>
         <v>5</v>
       </c>
-      <c r="T8" s="16" t="s">
+      <c r="T8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U8" s="16" t="n">
+      <c r="U8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="17" t="s">
+      <c r="V8" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="W8" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z8" s="16" t="s">
+      <c r="W8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z8" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AA8" s="16" t="n">
+      <c r="AA8" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="AB8" s="16" t="n">
+      <c r="AB8" s="1" t="n">
         <f aca="false">Y8+AA8/2</f>
         <v>15.5</v>
       </c>
-      <c r="AC8" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD8" s="20" t="n">
+      <c r="AC8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD8" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U8,W8,X8,AB8,AC8),0)</f>
         <v>6</v>
       </c>
-      <c r="AE8" s="20" t="n">
+      <c r="AE8" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S8,AD8),0)</f>
         <v>6</v>
       </c>
-      <c r="AF8" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG8" s="20" t="n">
+      <c r="AF8" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG8" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="AH8" s="20" t="n">
+      <c r="AH8" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="AI8" s="20" t="n">
+      <c r="AI8" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="AJ8" s="16" t="n">
+      <c r="AJ8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AK8" s="16" t="s">
+      <c r="AK8" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="9" s="16" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="n">
+    <row r="9" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="D9" s="18" t="n">
+      <c r="C9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>45988</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="4" t="n">
         <v>45988</v>
       </c>
-      <c r="G9" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="H9" s="18" t="n">
+      <c r="G9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" s="4" t="n">
         <v>45849</v>
       </c>
-      <c r="I9" s="16" t="n">
+      <c r="I9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="4" t="n">
         <v>46002</v>
       </c>
-      <c r="K9" s="16" t="n">
+      <c r="K9" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="L9" s="18" t="n">
+      <c r="L9" s="4" t="n">
         <v>45849</v>
       </c>
-      <c r="M9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="16" t="n">
+      <c r="M9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1" t="n">
         <f aca="false">ROUND(K9+M9/2,0)</f>
         <v>5</v>
       </c>
-      <c r="O9" s="16" t="n">
+      <c r="O9" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C9,E9,G9,I9,N9),0)</f>
         <v>7</v>
       </c>
-      <c r="P9" s="16" t="str">
+      <c r="P9" s="1" t="str">
         <f aca="false">IF(O9&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q9" s="16" t="n">
+      <c r="Q9" s="1" t="n">
         <v>0.8</v>
       </c>
-      <c r="R9" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="S9" s="20" t="n">
+      <c r="R9" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="S9" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q9:R9,O9),0)</f>
         <v>5</v>
       </c>
-      <c r="T9" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="U9" s="16" t="n">
+      <c r="T9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="U9" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="V9" s="17" t="s">
+      <c r="V9" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="W9" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA9" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB9" s="16" t="n">
+      <c r="W9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB9" s="1" t="n">
         <f aca="false">Y9+AA9/2</f>
         <v>15</v>
       </c>
-      <c r="AC9" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD9" s="20" t="n">
+      <c r="AC9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD9" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U9,W9,X9,AB9,AC9),0)</f>
         <v>6</v>
       </c>
-      <c r="AE9" s="20" t="n">
+      <c r="AE9" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S9,AD9),0)</f>
         <v>6</v>
       </c>
-      <c r="AF9" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG9" s="20" t="n">
+      <c r="AF9" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG9" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(C9,E9,G9,I9,K9),0)</f>
         <v>7</v>
       </c>
-      <c r="AH9" s="20" t="n">
+      <c r="AH9" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U9,AF9),0)</f>
         <v>8</v>
       </c>
-      <c r="AI9" s="20" t="n">
+      <c r="AI9" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(AG9,AH9),0)</f>
         <v>7</v>
       </c>
-      <c r="AJ9" s="16" t="n">
+      <c r="AJ9" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AK9" s="16" t="s">
+      <c r="AK9" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="10" s="16" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="17" t="s">
+    <row r="10" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="4" t="n">
         <v>45855</v>
       </c>
-      <c r="G10" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="I10" s="16" t="n">
+      <c r="G10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="K10" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L10" s="18" t="n">
+      <c r="K10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" s="4" t="n">
         <v>46001</v>
       </c>
-      <c r="M10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="16" t="n">
+      <c r="M10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1" t="n">
         <f aca="false">ROUND(K10+M10/2,0)</f>
         <v>8</v>
       </c>
-      <c r="O10" s="16" t="n">
+      <c r="O10" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C10,E10,G10,I10,N10),0)</f>
         <v>8</v>
       </c>
-      <c r="P10" s="16" t="str">
+      <c r="P10" s="1" t="str">
         <f aca="false">IF(O10&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q10" s="16" t="n">
+      <c r="Q10" s="1" t="n">
         <v>1.6</v>
       </c>
-      <c r="R10" s="19" t="n">
+      <c r="R10" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="S10" s="20" t="n">
+      <c r="S10" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q10:R10,O10),0)</f>
         <v>6</v>
       </c>
-      <c r="T10" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="U10" s="16" t="n">
+      <c r="T10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="U10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="V10" s="17" t="s">
+      <c r="V10" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="W10" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA10" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB10" s="16" t="n">
+      <c r="W10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB10" s="1" t="n">
         <f aca="false">Y10+AA10/2</f>
         <v>13</v>
       </c>
-      <c r="AC10" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD10" s="20" t="n">
+      <c r="AC10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD10" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U10,W10,X10,AB10,AC10),0)</f>
         <v>6</v>
       </c>
-      <c r="AE10" s="20" t="n">
+      <c r="AE10" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S10,AD10),0)</f>
         <v>6</v>
       </c>
-      <c r="AF10" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG10" s="20" t="n">
+      <c r="AF10" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG10" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(C10,E10,G10,I10,K10),0)</f>
         <v>8</v>
       </c>
-      <c r="AH10" s="20" t="n">
+      <c r="AH10" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U10,AF10),0)</f>
         <v>8</v>
       </c>
-      <c r="AI10" s="20" t="n">
+      <c r="AI10" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(AG10,AH10),0)</f>
         <v>8</v>
       </c>
-      <c r="AJ10" s="16" t="n">
+      <c r="AJ10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AK10" s="16" t="s">
+      <c r="AK10" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="11" s="21" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="n">
+    <row r="11" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16" t="n">
+      <c r="C11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="4" t="n">
         <v>45782</v>
       </c>
-      <c r="G11" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" s="18" t="n">
+      <c r="G11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" s="4" t="n">
         <v>45774</v>
       </c>
-      <c r="K11" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16" t="n">
+      <c r="K11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M11" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="16" t="n">
+      <c r="N11" s="1" t="n">
         <f aca="false">ROUND(K11+M11/2,0)</f>
         <v>14</v>
       </c>
-      <c r="O11" s="16" t="n">
+      <c r="O11" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C11,E11,G11,I11,N11),0)</f>
         <v>9</v>
       </c>
-      <c r="P11" s="16" t="str">
+      <c r="P11" s="1" t="str">
         <f aca="false">IF(O11&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q11" s="16" t="n">
+      <c r="Q11" s="1" t="n">
         <v>8.6</v>
       </c>
-      <c r="R11" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="S11" s="20" t="n">
+      <c r="R11" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S11" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q11:R11,O11),0)</f>
         <v>9</v>
       </c>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16" t="n">
+      <c r="U11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="17" t="s">
+      <c r="V11" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="W11" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="X11" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y11" s="16" t="n">
+      <c r="W11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="16" t="n">
+      <c r="AA11" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="AB11" s="16" t="n">
+      <c r="AB11" s="1" t="n">
         <f aca="false">Y11+AA11/2</f>
         <v>14.5</v>
       </c>
-      <c r="AC11" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD11" s="20" t="n">
+      <c r="AC11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U11,W11,X11,AB11,AC11),0)</f>
         <v>9</v>
       </c>
-      <c r="AE11" s="20" t="n">
+      <c r="AE11" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S11,AD11),0)</f>
         <v>9</v>
       </c>
-      <c r="AF11" s="20"/>
-    </row>
-    <row r="12" s="21" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="17" t="s">
+      <c r="AF11" s="13"/>
+      <c r="AG11" s="13"/>
+      <c r="AH11" s="13"/>
+      <c r="AI11" s="13"/>
+    </row>
+    <row r="12" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16" t="n">
+      <c r="C12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="H12" s="18" t="n">
+      <c r="G12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" s="4" t="n">
         <v>45849</v>
       </c>
-      <c r="I12" s="16" t="n">
+      <c r="I12" s="1" t="n">
         <f aca="false">ROUND(MAX(G13,E13),0)</f>
         <v>8</v>
       </c>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16" t="n">
+      <c r="K12" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="L12" s="18" t="n">
+      <c r="L12" s="4" t="n">
         <v>45849</v>
       </c>
-      <c r="M12" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="16" t="n">
+      <c r="M12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1" t="n">
         <f aca="false">ROUND(K12+M12/2,0)</f>
         <v>8</v>
       </c>
-      <c r="O12" s="16" t="n">
+      <c r="O12" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C12,E12,G12,I12,N12),0)</f>
         <v>8</v>
       </c>
-      <c r="P12" s="16" t="str">
+      <c r="P12" s="1" t="str">
         <f aca="false">IF(O12&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q12" s="16" t="n">
+      <c r="Q12" s="1" t="n">
         <v>2.1</v>
       </c>
-      <c r="R12" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="S12" s="20" t="n">
+      <c r="R12" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S12" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q12:R12,O12),0)</f>
         <v>7</v>
       </c>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16" t="n">
+      <c r="U12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="17" t="s">
+      <c r="V12" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="W12" s="16" t="n">
+      <c r="W12" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X12" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y12" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z12" s="16" t="s">
+      <c r="X12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z12" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="AA12" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB12" s="16" t="n">
+      <c r="AA12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB12" s="1" t="n">
         <f aca="false">Y12+AA12/2</f>
         <v>15</v>
       </c>
-      <c r="AC12" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD12" s="20" t="n">
+      <c r="AC12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD12" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U12,W12,X12,AB12,AC12),0)</f>
         <v>9</v>
       </c>
-      <c r="AE12" s="20" t="n">
+      <c r="AE12" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S12,AD12),0)</f>
         <v>8</v>
       </c>
-      <c r="AF12" s="20"/>
-    </row>
-    <row r="13" s="16" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="n">
+      <c r="AF12" s="13"/>
+      <c r="AG12" s="13"/>
+      <c r="AH12" s="13"/>
+      <c r="AI12" s="13"/>
+    </row>
+    <row r="13" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" s="18" t="n">
+      <c r="C13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" s="4" t="n">
         <v>45988</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G13" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="H13" s="18" t="n">
+      <c r="G13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>45849</v>
       </c>
-      <c r="I13" s="16" t="n">
+      <c r="I13" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="4" t="n">
         <v>45849</v>
       </c>
-      <c r="K13" s="16" t="n">
+      <c r="K13" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="L13" s="18" t="n">
+      <c r="L13" s="4" t="n">
         <v>45988</v>
       </c>
-      <c r="M13" s="16" t="n">
+      <c r="M13" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="N13" s="16" t="n">
+      <c r="N13" s="1" t="n">
         <f aca="false">ROUND(K13+M13/2,0)</f>
         <v>20</v>
       </c>
-      <c r="O13" s="16" t="n">
+      <c r="O13" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C13,E13,G13,I13,N13),0)</f>
         <v>9</v>
       </c>
-      <c r="P13" s="16" t="str">
+      <c r="P13" s="1" t="str">
         <f aca="false">IF(O13&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q13" s="16" t="n">
+      <c r="Q13" s="1" t="n">
         <v>2.8</v>
       </c>
-      <c r="R13" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="S13" s="20" t="n">
+      <c r="R13" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="S13" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q13:R13,O13),0)</f>
         <v>7</v>
       </c>
-      <c r="T13" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="U13" s="16" t="n">
+      <c r="T13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="U13" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V13" s="17" t="s">
+      <c r="V13" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="W13" s="16" t="n">
+      <c r="W13" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="X13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="16" t="n">
+      <c r="X13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AA13" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB13" s="16" t="n">
+      <c r="AA13" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB13" s="1" t="n">
         <f aca="false">Y13+AA13/2</f>
         <v>14</v>
       </c>
-      <c r="AC13" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD13" s="20" t="n">
+      <c r="AC13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD13" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U13,W13,X13,AB13,AC13),0)</f>
         <v>7</v>
       </c>
-      <c r="AE13" s="20" t="n">
+      <c r="AE13" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S13,AD13),0)</f>
         <v>7</v>
       </c>
-      <c r="AF13" s="20"/>
-      <c r="AG13" s="20"/>
-      <c r="AH13" s="20"/>
-      <c r="AI13" s="20"/>
-    </row>
-    <row r="14" s="16" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="n">
+      <c r="AF13" s="13"/>
+      <c r="AG13" s="13"/>
+      <c r="AH13" s="13"/>
+      <c r="AI13" s="13"/>
+    </row>
+    <row r="14" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="4" t="n">
         <v>45988</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="4" t="n">
         <v>45978</v>
       </c>
-      <c r="G14" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="I14" s="16" t="n">
+      <c r="G14" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="K14" s="16" t="n">
+      <c r="K14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M14" s="16" t="n">
+      <c r="M14" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="N14" s="16" t="n">
+      <c r="N14" s="1" t="n">
         <f aca="false">ROUND(K14+M14/2,0)</f>
         <v>15</v>
       </c>
-      <c r="O14" s="16" t="n">
+      <c r="O14" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C14,E14,G14,I14,N14),0)</f>
         <v>9</v>
       </c>
-      <c r="P14" s="16" t="str">
+      <c r="P14" s="1" t="str">
         <f aca="false">IF(O14&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q14" s="16" t="n">
+      <c r="Q14" s="1" t="n">
         <v>2.4</v>
       </c>
-      <c r="R14" s="19" t="n">
+      <c r="R14" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="S14" s="20" t="n">
+      <c r="S14" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q14:R14,O14),0)</f>
         <v>7</v>
       </c>
-      <c r="T14" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="U14" s="16" t="n">
+      <c r="T14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="U14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="V14" s="17" t="s">
+      <c r="V14" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="W14" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="16" t="n">
+      <c r="W14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z14" s="16" t="s">
+      <c r="Z14" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="AA14" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB14" s="16" t="n">
+      <c r="AA14" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB14" s="1" t="n">
         <f aca="false">Y14+AA14/2</f>
         <v>14</v>
       </c>
-      <c r="AC14" s="16" t="n">
+      <c r="AC14" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AD14" s="20" t="n">
+      <c r="AD14" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U14,W14,X14,AB14,AC14),0)</f>
         <v>6</v>
       </c>
-      <c r="AE14" s="20" t="n">
+      <c r="AE14" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S14,AD14),0)</f>
         <v>7</v>
       </c>
-      <c r="AF14" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG14" s="20" t="n">
+      <c r="AF14" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(C14,E14,G14,I14,K14),0)</f>
         <v>7</v>
       </c>
-      <c r="AH14" s="20" t="n">
+      <c r="AH14" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U14,AF14),0)</f>
         <v>8</v>
       </c>
-      <c r="AI14" s="20" t="n">
+      <c r="AI14" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(AG14,AH14),0)</f>
         <v>8</v>
       </c>
-      <c r="AJ14" s="16" t="n">
+      <c r="AJ14" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AK14" s="16" t="s">
+      <c r="AK14" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="15" s="16" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="n">
+    <row r="15" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="4" t="n">
         <v>45988</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="4" t="n">
         <v>45978</v>
       </c>
-      <c r="G15" s="16" t="n">
+      <c r="G15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="H15" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="I15" s="16" t="n">
+      <c r="I15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="K15" s="16" t="n">
+      <c r="K15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M15" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" s="16" t="n">
+      <c r="M15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1" t="n">
         <f aca="false">ROUND(K15+M15/2,0)</f>
         <v>8</v>
       </c>
-      <c r="O15" s="16" t="n">
+      <c r="O15" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C15,E15,G15,I15,N15),0)</f>
         <v>7</v>
       </c>
-      <c r="P15" s="16" t="str">
+      <c r="P15" s="1" t="str">
         <f aca="false">IF(O15&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="Q15" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="S15" s="20" t="n">
+      <c r="Q15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S15" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q15:R15,O15),0)</f>
         <v>6</v>
       </c>
-      <c r="T15" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="U15" s="16" t="n">
+      <c r="T15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="U15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="V15" s="17" t="s">
+      <c r="V15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="W15" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA15" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB15" s="16" t="n">
+      <c r="W15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB15" s="1" t="n">
         <f aca="false">Y15+AA15/2</f>
         <v>13</v>
       </c>
-      <c r="AC15" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD15" s="20" t="n">
+      <c r="AC15" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD15" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U15,W15,X15,AB15,AC15),0)</f>
         <v>6</v>
       </c>
-      <c r="AE15" s="20" t="n">
+      <c r="AE15" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S15,AD15),0)</f>
         <v>6</v>
       </c>
-      <c r="AF15" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG15" s="20" t="n">
+      <c r="AF15" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG15" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(C15,E15,G15,I15,K15),0)</f>
         <v>7</v>
       </c>
-      <c r="AH15" s="20" t="n">
+      <c r="AH15" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U15,AF15),0)</f>
         <v>9</v>
       </c>
-      <c r="AI15" s="20" t="n">
+      <c r="AI15" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(AG15,AH15),0)</f>
         <v>8</v>
       </c>
-      <c r="AJ15" s="16" t="n">
+      <c r="AJ15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AK15" s="16" t="s">
+      <c r="AK15" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" s="17" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="n">
+    <row r="16" s="3" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="16" t="n">
+      <c r="C16" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1" t="n">
         <f aca="false">ROUND(K16+M16/2,0)</f>
         <v>1</v>
       </c>
-      <c r="O16" s="16" t="n">
+      <c r="O16" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C16,E16,G16,I16,N16),0)</f>
         <v>2</v>
       </c>
-      <c r="P16" s="16" t="str">
+      <c r="P16" s="1" t="str">
         <f aca="false">IF(O16&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="Q16" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" s="19" t="n">
+      <c r="Q16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="S16" s="20" t="n">
+      <c r="S16" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q16:R16,O16),0)</f>
         <v>3</v>
       </c>
-      <c r="T16" s="16" t="s">
+      <c r="T16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U16" s="16" t="n">
+      <c r="U16" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V16" s="16" t="s">
+      <c r="V16" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="W16" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="16" t="s">
+      <c r="W16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="AA16" s="16" t="n">
+      <c r="AA16" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="AB16" s="16" t="n">
+      <c r="AB16" s="1" t="n">
         <f aca="false">Y16+AA16/2</f>
         <v>0.5</v>
       </c>
-      <c r="AC16" s="16" t="n">
+      <c r="AC16" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AD16" s="20" t="n">
+      <c r="AD16" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U16,W16,X16,AB16,AC16),0)</f>
         <v>2</v>
       </c>
-      <c r="AE16" s="20" t="n">
+      <c r="AE16" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S16,AD16),0)</f>
         <v>3</v>
       </c>
-      <c r="AF16" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG16" s="20" t="n">
+      <c r="AF16" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG16" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(C16,E16,G16,I16,K16),0)</f>
         <v>2</v>
       </c>
-      <c r="AH16" s="20" t="n">
+      <c r="AH16" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U16,AF16),0)</f>
         <v>6</v>
       </c>
-      <c r="AI16" s="20" t="n">
+      <c r="AI16" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(AG16,AH16),0)</f>
         <v>4</v>
       </c>
-      <c r="AJ16" s="17" t="n">
+      <c r="AJ16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AK16" s="17" t="s">
+      <c r="AK16" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" s="17" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="n">
+    <row r="17" s="3" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16" t="n">
+      <c r="C17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="N17" s="16" t="n">
+      <c r="N17" s="1" t="n">
         <f aca="false">ROUND(K17+M17/2,0)</f>
         <v>2</v>
       </c>
-      <c r="O17" s="16" t="n">
+      <c r="O17" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C17,E17,G17,I17,N17),0)</f>
         <v>1</v>
       </c>
-      <c r="P17" s="16" t="str">
+      <c r="P17" s="1" t="str">
         <f aca="false">IF(O17&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="Q17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="20" t="n">
+      <c r="Q17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q17:R17,O17),0)</f>
         <v>1</v>
       </c>
-      <c r="T17" s="16" t="s">
+      <c r="T17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="16" t="n">
+      <c r="U17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="1" t="n">
         <f aca="false">Y17+AA17/2</f>
         <v>1</v>
       </c>
-      <c r="AC17" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD17" s="20" t="n">
+      <c r="AC17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U17,W17,X17,AB17,AC17),0)</f>
         <v>1</v>
       </c>
-      <c r="AE17" s="20" t="n">
+      <c r="AE17" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S17,AD17),0)</f>
         <v>1</v>
       </c>
-      <c r="AF17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="20" t="n">
+      <c r="AF17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(C17,E17,G17,I17,K17),0)</f>
         <v>1</v>
       </c>
-      <c r="AH17" s="20" t="n">
+      <c r="AH17" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U17,AF17),0)</f>
         <v>1</v>
       </c>
-      <c r="AI17" s="20" t="n">
+      <c r="AI17" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(AG17,AH17),0)</f>
         <v>1</v>
       </c>
-      <c r="AJ17" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK17" s="17" t="s">
+      <c r="AJ17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" s="3" t="s">
         <v>125</v>
       </c>
     </row>
@@ -6394,10 +6336,10 @@
       <c r="Q18" s="1" t="n">
         <v>1.8</v>
       </c>
-      <c r="R18" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="S18" s="15" t="n">
+      <c r="R18" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S18" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(Q18:R18,O18),0)</f>
         <v>7</v>
       </c>
@@ -6429,15 +6371,15 @@
       <c r="AC18" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AD18" s="15" t="n">
+      <c r="AD18" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(U18,W18,X18,AB18,AC18),0)</f>
         <v>7</v>
       </c>
-      <c r="AE18" s="15" t="n">
+      <c r="AE18" s="13" t="n">
         <f aca="false">ROUND(AVERAGE(S18,AD18),0)</f>
         <v>7</v>
       </c>
-      <c r="AF18" s="15"/>
+      <c r="AF18" s="13"/>
       <c r="AH18" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(U18,AF18),0)</f>
         <v>4</v>
